--- a/custom/data/wilayah/wilayah_dm31_2026.xlsx
+++ b/custom/data/wilayah/wilayah_dm31_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lee-uluk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suku" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldeia" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Postu" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Lee-uluk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Suku" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Aldeia" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Postu" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Suku'!$A$1:$K$473</definedName>
@@ -44,7 +44,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,11 @@
         <fgColor rgb="00FFF3B0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DFF5E8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -74,12 +79,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -468,7 +474,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Suku: 472 · Aldeia: 2250 · Postu: 71 · Suku VERIFIKA: 57</t>
+          <t>Suku: 472 · Aldeia: 2250 · Postu: 71 · Suku VERIFIKA: 0 (prenxe ona 57 tuir fonte web — haree kolun obs)</t>
         </is>
       </c>
     </row>
@@ -478,7 +484,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1. Aba "Suku": liña kór-mean (verifika = SIN) → hakerek postu_code (haree aba "Postu" ka kolun sujestaun).</t>
+          <t>1. Aba "Suku": liña kór-mean (verifika = SIN) → hakerek postu_code. Liña kór-verde (verifika = WEB/DIPLOMA) prenxe ona tuir fonte iha kolun obs.</t>
         </is>
       </c>
     </row>
@@ -621,12 +627,9 @@
           <t>Aileu Vila</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>5</v>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -662,12 +665,9 @@
           <t>Aileu Vila</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>3</v>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -703,12 +703,9 @@
           <t>Aileu Vila</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>5</v>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -744,12 +741,9 @@
           <t>Aileu Vila</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>7</v>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -785,12 +779,9 @@
           <t>Aileu Vila</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>4</v>
       </c>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -826,12 +817,9 @@
           <t>Aileu Vila</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>5</v>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -867,12 +855,9 @@
           <t>Aileu Vila</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>5</v>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -908,12 +893,9 @@
           <t>Aileu Vila</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>3</v>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -949,12 +931,9 @@
           <t>Aileu Vila</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>4</v>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -990,8 +969,6 @@
           <t>Aileu Vila</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
         <v>3</v>
       </c>
@@ -1035,8 +1012,6 @@
           <t>Aileu Vila</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
         <v>8</v>
       </c>
@@ -1080,12 +1055,9 @@
           <t>Aileu Vila</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
         <v>3</v>
       </c>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1121,12 +1093,9 @@
           <t>Aileu Vila</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
         <v>10</v>
       </c>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1162,983 +1131,1228 @@
           <t>Aileu Vila</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
         <v>4</v>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>AIL-S015</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Acumau</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>AIL-04</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Remexio</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio (ka AIL-01 Aileu Vila)</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="J16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Remexio_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0104__remexio</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>AIL-S016</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Aicurus</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>AIL-04</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Remexio</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J17" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Novo Suco</t>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Novo Suco; Aicurus uluk aldeia husi suco Tulataqueo (Remexio); Fonte postu: https://de.wikipedia.org/wiki/Tulataqueo</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>AIL-S017</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Karahili</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>AIL-04</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Remexio</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="J18" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K18" s="4" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Suku Karahili iha Postu Remexio; Fonte postu: https://timorpost.com/jeral-tl/tp-54977/pnds-postu-remexio-ho-ks-estabelese-es-pnds-iha-suku-karahili/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>AIL-S018</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Suco Liurai</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>AIL-04</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Remexio</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Naran hanesan ho suco seluk iha munisípiu ne'e (kódigu la hanesan; PDF la hakerek I/II)</t>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Naran hanesan ho suco seluk iha munisípiu ne'e (kódigu la hanesan; PDF la hakerek I/II); Fonte postu: https://en.wikipedia.org/wiki/Remexio_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0104__remexio</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>AIL-S019</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Tulataqueo</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>AIL-04</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Remexio</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="J20" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="K20" s="4" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Remexio_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0104__remexio</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>AIL-S020</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Fadabloco</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>AIL-04</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Remexio</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="J21" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K21" s="4" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Remexio_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0104__remexio</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>AIL-S021</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Faturaca</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>AIL-04</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Remexio</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="J22" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Fonte web hakerek "Faturasa"; Fonte postu: https://en.wikipedia.org/wiki/Remexio_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0104__remexio</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>AIL-S022</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Maumeta</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>AIL-04</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Remexio</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="J23" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Remexio_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0104__remexio</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>AIL-S023</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Hautoho</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>AIL-04</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Remexio</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="J24" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Remexio_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0104__remexio</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>AIL-S024</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Fahisoi</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>AIL-04</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Remexio</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="J25" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Naran hanesan ho suco seluk iha munisípiu ne'e (kódigu la hanesan; PDF la hakerek I/II)</t>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Naran hanesan ho suco seluk iha munisípiu ne'e (kódigu la hanesan; PDF la hakerek I/II); Fonte postu: https://en.wikipedia.org/wiki/Remexio_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0104__remexio</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>AIL-S025</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Acubilitoho</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>AIL-03</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Lequidoe</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
+      <c r="J26" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Kolun NO ALDEIA mamuk iha PDF (konta husi tabela)</t>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Kolun NO ALDEIA mamuk iha PDF (konta husi tabela); Fonte postu: https://en.wikipedia.org/wiki/Lequidoe_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0103__lequidoe</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C27" s="4" t="n">
+      <c r="C27" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>AIL-S026</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Betulau</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>AIL-03</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Lequidoe</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="J27" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Kolun NO ALDEIA mamuk iha PDF (konta husi tabela)</t>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Kolun NO ALDEIA mamuk iha PDF (konta husi tabela); Fonte postu: https://en.wikipedia.org/wiki/Lequidoe_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0103__lequidoe</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>AIL-S027</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Bereleu</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>AIL-03</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Lequidoe</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n">
+      <c r="J28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Kolun NO ALDEIA mamuk iha PDF (konta husi tabela)</t>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>Kolun NO ALDEIA mamuk iha PDF (konta husi tabela); Fonte postu: https://en.wikipedia.org/wiki/Lequidoe_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0103__lequidoe</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>AIL-S028</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Fahisoi</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr"/>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>AIL-03</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Lequidoe</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
+      <c r="J29" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Naran hanesan ho suco seluk iha munisípiu ne'e (kódigu la hanesan; PDF la hakerek I/II)</t>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Naran hanesan ho suco seluk iha munisípiu ne'e (kódigu la hanesan; PDF la hakerek I/II); Fonte postu: https://en.wikipedia.org/wiki/Lequidoe_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0103__lequidoe</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>AIL-S029</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Faturilau</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>AIL-03</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Lequidoe</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
+      <c r="J30" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="K30" s="4" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Lequidoe_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0103__lequidoe</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>AIL-S030</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Manucassa</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>AIL-03</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Lequidoe</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
+      <c r="J31" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="K31" s="4" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Lequidoe_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0103__lequidoe</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>AIL-S031</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Namolesso</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>AIL-03</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Lequidoe</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n">
+      <c r="J32" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K32" s="4" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Lequidoe_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0103__lequidoe</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>AIL-S032</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Bocolelo</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>AIL-02</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Laulara</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="J33" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K33" s="4" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Laulara_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0102__laulara/</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>AIL-S033</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Cotolau</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>AIL-02</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Laulara</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J34" s="4" t="n">
+      <c r="J34" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K34" s="4" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Laulara_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0102__laulara/</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C35" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>AIL-S034</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Talitu</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>AIL-02</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Laulara</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="J35" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="4" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Laulara_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0102__laulara/</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>AIL-S035</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Madabeno</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>AIL-02</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Laulara</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n">
+      <c r="J36" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="K36" s="4" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Laulara_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0102__laulara/</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>AIL-S036</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Tohumeta</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>AIL-02</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Laulara</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="J37" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K37" s="4" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Laulara_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0102__laulara/</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>AIL</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Aileu</t>
         </is>
       </c>
-      <c r="C38" s="4" t="n">
+      <c r="C38" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>AIL-S037</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>Fatisi</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>AIL-02</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Laulara</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: AIL-02 Laulara / AIL-03 Lequidoe / AIL-04 Remexio</t>
         </is>
       </c>
-      <c r="J38" s="4" t="n">
+      <c r="J38" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K38" s="4" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Laulara_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0102__laulara/</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2174,12 +2388,9 @@
           <t>Ainaro</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
         <v>7</v>
       </c>
-      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2215,12 +2426,9 @@
           <t>Ainaro</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
         <v>5</v>
       </c>
-      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2256,12 +2464,9 @@
           <t>Ainaro</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
         <v>4</v>
       </c>
-      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2297,12 +2502,9 @@
           <t>Ainaro</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
         <v>3</v>
       </c>
-      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2338,12 +2540,9 @@
           <t>Ainaro</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
         <v>5</v>
       </c>
-      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2379,12 +2578,9 @@
           <t>Ainaro</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2420,12 +2616,9 @@
           <t>Ainaro</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
         <v>4</v>
       </c>
-      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2461,12 +2654,9 @@
           <t>Maubisse</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
         <v>9</v>
       </c>
-      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2502,12 +2692,9 @@
           <t>Maubisse</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
         <v>6</v>
       </c>
-      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2543,12 +2730,9 @@
           <t>Maubisse</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
         <v>6</v>
       </c>
-      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2584,12 +2768,9 @@
           <t>Maubisse</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
         <v>4</v>
       </c>
-      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2625,12 +2806,9 @@
           <t>Maubisse</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
         <v>4</v>
       </c>
-      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2666,12 +2844,9 @@
           <t>Maubisse</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
         <v>4</v>
       </c>
-      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2707,12 +2882,9 @@
           <t>Maubisse</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
         <v>7</v>
       </c>
-      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2748,12 +2920,9 @@
           <t>Maubisse</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="n">
         <v>12</v>
       </c>
-      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2789,12 +2958,9 @@
           <t>Maubisse</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
         <v>10</v>
       </c>
-      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2830,12 +2996,9 @@
           <t>Hatu-Builico</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
         <v>5</v>
       </c>
-      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2871,12 +3034,9 @@
           <t>Hatu-Builico</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
         <v>8</v>
       </c>
-      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2912,12 +3072,9 @@
           <t>Hatu-Builico</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
         <v>8</v>
       </c>
-      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2953,12 +3110,9 @@
           <t>Hatudo</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
         <v>6</v>
       </c>
-      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2994,12 +3148,9 @@
           <t>Hatudo</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
         <v>10</v>
       </c>
-      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3035,12 +3186,9 @@
           <t>Ataúro</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
         <v>4</v>
       </c>
-      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3076,12 +3224,9 @@
           <t>Ataúro</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
         <v>4</v>
       </c>
-      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3117,12 +3262,9 @@
           <t>Ataúro</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
         <v>4</v>
       </c>
-      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3158,12 +3300,9 @@
           <t>Ataúro</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="n">
         <v>4</v>
       </c>
-      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3199,12 +3338,9 @@
           <t>Ataúro</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="n">
         <v>3</v>
       </c>
-      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3240,12 +3376,9 @@
           <t>Baguia</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
         <v>4</v>
       </c>
-      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3281,12 +3414,9 @@
           <t>Baguia</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
         <v>5</v>
       </c>
-      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3322,12 +3452,9 @@
           <t>Baguia</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
         <v>5</v>
       </c>
-      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3363,12 +3490,9 @@
           <t>Baguia</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
         <v>4</v>
       </c>
-      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3404,12 +3528,9 @@
           <t>Baguia</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="n">
         <v>6</v>
       </c>
-      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3445,12 +3566,9 @@
           <t>Baguia</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="n">
         <v>7</v>
       </c>
-      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3486,12 +3604,9 @@
           <t>Baguia</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="n">
         <v>5</v>
       </c>
-      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3527,12 +3642,9 @@
           <t>Baguia</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="n">
         <v>3</v>
       </c>
-      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3568,8 +3680,6 @@
           <t>Baguia</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="n">
         <v>4</v>
       </c>
@@ -3613,12 +3723,9 @@
           <t>Baguia</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="n">
         <v>4</v>
       </c>
-      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3654,12 +3761,9 @@
           <t>Baucau</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="n">
         <v>5</v>
       </c>
-      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3695,12 +3799,9 @@
           <t>Baucau</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="n">
         <v>6</v>
       </c>
-      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3736,12 +3837,9 @@
           <t>Baucau</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="n">
         <v>2</v>
       </c>
-      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3777,12 +3875,9 @@
           <t>Baucau</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="n">
         <v>4</v>
       </c>
-      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3818,12 +3913,9 @@
           <t>Baucau</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="n">
         <v>4</v>
       </c>
-      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3859,12 +3951,9 @@
           <t>Baucau</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="n">
         <v>3</v>
       </c>
-      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3900,12 +3989,9 @@
           <t>Baucau</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="n">
         <v>4</v>
       </c>
-      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3941,12 +4027,9 @@
           <t>Baucau</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="n">
         <v>8</v>
       </c>
-      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3982,12 +4065,9 @@
           <t>Baucau</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="n">
         <v>5</v>
       </c>
-      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4023,8 +4103,6 @@
           <t>Baucau</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="n">
         <v>4</v>
       </c>
@@ -4068,12 +4146,9 @@
           <t>Baucau</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="n">
         <v>6</v>
       </c>
-      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4109,12 +4184,9 @@
           <t>Baucau</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="n">
         <v>4</v>
       </c>
-      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4150,12 +4222,9 @@
           <t>Baucau</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="n">
         <v>10</v>
       </c>
-      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4191,12 +4260,9 @@
           <t>Laga</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="n">
         <v>10</v>
       </c>
-      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4232,12 +4298,9 @@
           <t>Laga</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
         <v>5</v>
       </c>
-      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4273,12 +4336,9 @@
           <t>Laga</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="n">
         <v>5</v>
       </c>
-      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4314,12 +4374,9 @@
           <t>Laga</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="n">
         <v>9</v>
       </c>
-      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4355,12 +4412,9 @@
           <t>Laga</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="n">
         <v>11</v>
       </c>
-      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4396,8 +4450,6 @@
           <t>Laga</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="n">
         <v>6</v>
       </c>
@@ -4441,12 +4493,9 @@
           <t>Laga</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
         <v>1</v>
       </c>
-      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4482,53 +4531,62 @@
           <t>Laga</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="n">
         <v>6</v>
       </c>
-      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>BAU</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>Baucau</t>
         </is>
       </c>
-      <c r="C96" s="4" t="n">
+      <c r="C96" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>BAU-S095</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t>Tequinaumata</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr"/>
-      <c r="G96" s="4" t="inlineStr"/>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>BAU-03</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>Laga</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: BAU-03 Laga / BAU-04 Quelicai</t>
         </is>
       </c>
-      <c r="J96" s="4" t="n">
+      <c r="J96" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K96" s="4" t="inlineStr"/>
+      <c r="K96" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Laga_Administrative_Post ; https://citypopulation.de/en/timor/admin/0303__laga/</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4564,12 +4622,9 @@
           <t>Quelicai</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="n">
         <v>4</v>
       </c>
-      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4605,12 +4660,9 @@
           <t>Quelicai</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="n">
         <v>3</v>
       </c>
-      <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4646,12 +4698,9 @@
           <t>Quelicai</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="n">
         <v>2</v>
       </c>
-      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4687,12 +4736,9 @@
           <t>Quelicai</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="n">
         <v>3</v>
       </c>
-      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4728,12 +4774,9 @@
           <t>Quelicai</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="n">
         <v>5</v>
       </c>
-      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4769,12 +4812,9 @@
           <t>Quelicai</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="n">
         <v>3</v>
       </c>
-      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4810,12 +4850,9 @@
           <t>Quelicai</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="n">
         <v>4</v>
       </c>
-      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4851,12 +4888,9 @@
           <t>Quelicai Antigu</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="n">
         <v>3</v>
       </c>
-      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4892,12 +4926,9 @@
           <t>Quelicai Antigu</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="n">
         <v>5</v>
       </c>
-      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4933,12 +4964,9 @@
           <t>Quelicai Antigu</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="n">
         <v>4</v>
       </c>
-      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4974,12 +5002,9 @@
           <t>Matebian</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="n">
         <v>4</v>
       </c>
-      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5015,12 +5040,9 @@
           <t>Matebian</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="n">
         <v>4</v>
       </c>
-      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5056,12 +5078,9 @@
           <t>Matebian</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="n">
         <v>3</v>
       </c>
-      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5097,12 +5116,9 @@
           <t>Matebian</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="n">
         <v>4</v>
       </c>
-      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5138,12 +5154,9 @@
           <t>Matebian</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="n">
         <v>4</v>
       </c>
-      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5179,12 +5192,9 @@
           <t>Vemasse</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="n">
         <v>2</v>
       </c>
-      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5220,12 +5230,9 @@
           <t>Vemasse</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
         <v>3</v>
       </c>
-      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5261,12 +5268,9 @@
           <t>Vemasse</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="n">
         <v>5</v>
       </c>
-      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5302,12 +5306,9 @@
           <t>Vemasse</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="n">
         <v>3</v>
       </c>
-      <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5343,12 +5344,9 @@
           <t>Vemasse</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="n">
         <v>2</v>
       </c>
-      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5384,12 +5382,9 @@
           <t>Vemasse</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="n">
         <v>3</v>
       </c>
-      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5425,12 +5420,9 @@
           <t>Vemasse</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="n">
         <v>4</v>
       </c>
-      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5466,12 +5458,9 @@
           <t>Venilale</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="n">
         <v>5</v>
       </c>
-      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5507,12 +5496,9 @@
           <t>Venilale</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="n">
         <v>6</v>
       </c>
-      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5548,12 +5534,9 @@
           <t>Venilale</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="n">
         <v>4</v>
       </c>
-      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5589,12 +5572,9 @@
           <t>Venilale</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="n">
         <v>4</v>
       </c>
-      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5630,12 +5610,9 @@
           <t>Venilale</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="n">
         <v>4</v>
       </c>
-      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5671,12 +5648,9 @@
           <t>Venilale</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="n">
         <v>4</v>
       </c>
-      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5712,12 +5686,9 @@
           <t>Venilale</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="n">
         <v>4</v>
       </c>
-      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5753,12 +5724,9 @@
           <t>Venilale</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="n">
         <v>4</v>
       </c>
-      <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5794,12 +5762,9 @@
           <t>Atabae</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="n">
         <v>5</v>
       </c>
-      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5835,12 +5800,9 @@
           <t>Atabae</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="n">
         <v>4</v>
       </c>
-      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5876,12 +5838,9 @@
           <t>Atabae</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="n">
         <v>4</v>
       </c>
-      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5917,12 +5876,9 @@
           <t>Atabae</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="n">
         <v>7</v>
       </c>
-      <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5958,12 +5914,9 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="n">
         <v>5</v>
       </c>
-      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5999,12 +5952,9 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" t="n">
         <v>2</v>
       </c>
-      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6040,12 +5990,9 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="n">
         <v>2</v>
       </c>
-      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6081,12 +6028,9 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="n">
         <v>5</v>
       </c>
-      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6122,12 +6066,9 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="n">
         <v>2</v>
       </c>
-      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6163,12 +6104,9 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="n">
         <v>3</v>
       </c>
-      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6204,12 +6142,9 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="n">
         <v>6</v>
       </c>
-      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6245,12 +6180,9 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="n">
         <v>3</v>
       </c>
-      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6286,12 +6218,9 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="n">
         <v>2</v>
       </c>
-      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6327,12 +6256,9 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="n">
         <v>5</v>
       </c>
-      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6368,12 +6294,9 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" t="n">
         <v>4</v>
       </c>
-      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6409,12 +6332,9 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="n">
         <v>4</v>
       </c>
-      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6450,12 +6370,9 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" t="n">
         <v>5</v>
       </c>
-      <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6491,12 +6408,9 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" t="n">
         <v>3</v>
       </c>
-      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6532,12 +6446,9 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="n">
         <v>4</v>
       </c>
-      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6573,94 +6484,115 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" t="n">
         <v>3</v>
       </c>
-      <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="4" t="inlineStr">
+      <c r="A147" s="5" t="inlineStr">
         <is>
           <t>BOB</t>
         </is>
       </c>
-      <c r="B147" s="4" t="inlineStr">
+      <c r="B147" s="5" t="inlineStr">
         <is>
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="C147" s="4" t="n">
+      <c r="C147" s="5" t="n">
         <v>146</v>
       </c>
-      <c r="D147" s="4" t="inlineStr">
+      <c r="D147" s="5" t="inlineStr">
         <is>
           <t>BOB-S146</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
+      <c r="E147" s="5" t="inlineStr">
         <is>
           <t>Tebabui</t>
         </is>
       </c>
-      <c r="F147" s="4" t="inlineStr"/>
-      <c r="G147" s="4" t="inlineStr"/>
-      <c r="H147" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I147" s="4" t="inlineStr">
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>BOB-03</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>Bobonaro</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I147" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: BOB-03 Bobonaro / BOB-06 Maliana</t>
         </is>
       </c>
-      <c r="J147" s="4" t="n">
+      <c r="J147" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K147" s="4" t="inlineStr"/>
+      <c r="K147" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Bobonaro_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0403__bobonaro</t>
+        </is>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="4" t="inlineStr">
+      <c r="A148" s="5" t="inlineStr">
         <is>
           <t>BOB</t>
         </is>
       </c>
-      <c r="B148" s="4" t="inlineStr">
+      <c r="B148" s="5" t="inlineStr">
         <is>
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="C148" s="4" t="n">
+      <c r="C148" s="5" t="n">
         <v>147</v>
       </c>
-      <c r="D148" s="4" t="inlineStr">
+      <c r="D148" s="5" t="inlineStr">
         <is>
           <t>BOB-S147</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
+      <c r="E148" s="5" t="inlineStr">
         <is>
           <t>Oeleo</t>
         </is>
       </c>
-      <c r="F148" s="4" t="inlineStr"/>
-      <c r="G148" s="4" t="inlineStr"/>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I148" s="4" t="inlineStr">
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>BOB-03</t>
+        </is>
+      </c>
+      <c r="G148" s="5" t="inlineStr">
+        <is>
+          <t>Bobonaro</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I148" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: BOB-03 Bobonaro / BOB-06 Maliana</t>
         </is>
       </c>
-      <c r="J148" s="4" t="n">
+      <c r="J148" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="K148" s="4" t="inlineStr"/>
+      <c r="K148" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Bobonaro_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0403__bobonaro</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6696,12 +6628,9 @@
           <t>Maliana</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" t="n">
         <v>5</v>
       </c>
-      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6737,12 +6666,9 @@
           <t>Maliana</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="n">
         <v>3</v>
       </c>
-      <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6778,12 +6704,9 @@
           <t>Maliana</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="n">
         <v>12</v>
       </c>
-      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6819,12 +6742,9 @@
           <t>Maliana</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" t="n">
         <v>4</v>
       </c>
-      <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6860,12 +6780,9 @@
           <t>Maliana</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="n">
         <v>6</v>
       </c>
-      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6901,12 +6818,9 @@
           <t>Maliana</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="n">
         <v>6</v>
       </c>
-      <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6942,53 +6856,62 @@
           <t>Maliana</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
       <c r="J155" t="n">
         <v>3</v>
       </c>
-      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="4" t="inlineStr">
+      <c r="A156" s="5" t="inlineStr">
         <is>
           <t>BOB</t>
         </is>
       </c>
-      <c r="B156" s="4" t="inlineStr">
+      <c r="B156" s="5" t="inlineStr">
         <is>
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="C156" s="4" t="n">
+      <c r="C156" s="5" t="n">
         <v>155</v>
       </c>
-      <c r="D156" s="4" t="inlineStr">
+      <c r="D156" s="5" t="inlineStr">
         <is>
           <t>BOB-S155</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
+      <c r="E156" s="5" t="inlineStr">
         <is>
           <t>Raiheu</t>
         </is>
       </c>
-      <c r="F156" s="4" t="inlineStr"/>
-      <c r="G156" s="4" t="inlineStr"/>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I156" s="4" t="inlineStr">
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>BOB-04</t>
+        </is>
+      </c>
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>Cailaco</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I156" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: BOB-04 Cailaco / BOB-06 Maliana</t>
         </is>
       </c>
-      <c r="J156" s="4" t="n">
+      <c r="J156" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K156" s="4" t="inlineStr"/>
+      <c r="K156" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Cailaco_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7024,12 +6947,9 @@
           <t>Cailaco</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" t="n">
         <v>4</v>
       </c>
-      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7065,12 +6985,9 @@
           <t>Cailaco</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
       <c r="J158" t="n">
         <v>2</v>
       </c>
-      <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7106,12 +7023,9 @@
           <t>Cailaco</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" t="n">
         <v>3</v>
       </c>
-      <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7147,12 +7061,9 @@
           <t>Cailaco</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
       <c r="J160" t="n">
         <v>4</v>
       </c>
-      <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7188,12 +7099,9 @@
           <t>Cailaco</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
       <c r="J161" t="n">
         <v>3</v>
       </c>
-      <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7229,53 +7137,62 @@
           <t>Cailaco</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
       <c r="J162" t="n">
         <v>2</v>
       </c>
-      <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="4" t="inlineStr">
+      <c r="A163" s="5" t="inlineStr">
         <is>
           <t>BOB</t>
         </is>
       </c>
-      <c r="B163" s="4" t="inlineStr">
+      <c r="B163" s="5" t="inlineStr">
         <is>
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="C163" s="4" t="n">
+      <c r="C163" s="5" t="n">
         <v>162</v>
       </c>
-      <c r="D163" s="4" t="inlineStr">
+      <c r="D163" s="5" t="inlineStr">
         <is>
           <t>BOB-S162</t>
         </is>
       </c>
-      <c r="E163" s="4" t="inlineStr">
+      <c r="E163" s="5" t="inlineStr">
         <is>
           <t>Manapa</t>
         </is>
       </c>
-      <c r="F163" s="4" t="inlineStr"/>
-      <c r="G163" s="4" t="inlineStr"/>
-      <c r="H163" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I163" s="4" t="inlineStr">
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>BOB-04</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>Cailaco</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I163" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: BOB-04 Cailaco / BOB-05 Lolotoe</t>
         </is>
       </c>
-      <c r="J163" s="4" t="n">
+      <c r="J163" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K163" s="4" t="inlineStr"/>
+      <c r="K163" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Cailaco_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7311,12 +7228,9 @@
           <t>Lolotoe</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
       <c r="J164" t="n">
         <v>2</v>
       </c>
-      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7352,12 +7266,9 @@
           <t>Lolotoe</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
       <c r="J165" t="n">
         <v>2</v>
       </c>
-      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7393,12 +7304,9 @@
           <t>Lolotoe</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
       <c r="J166" t="n">
         <v>3</v>
       </c>
-      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7434,12 +7342,9 @@
           <t>Lolotoe</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
       <c r="J167" t="n">
         <v>3</v>
       </c>
-      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7475,12 +7380,9 @@
           <t>Lolotoe</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
       <c r="J168" t="n">
         <v>4</v>
       </c>
-      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7516,12 +7418,9 @@
           <t>Lolotoe</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
       <c r="J169" t="n">
         <v>3</v>
       </c>
-      <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7557,12 +7456,9 @@
           <t>Lolotoe</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
       <c r="J170" t="n">
         <v>3</v>
       </c>
-      <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7598,12 +7494,9 @@
           <t>Balibo</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
       <c r="J171" t="n">
         <v>3</v>
       </c>
-      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7639,12 +7532,9 @@
           <t>Balibo</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
       <c r="J172" t="n">
         <v>4</v>
       </c>
-      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7680,12 +7570,9 @@
           <t>Balibo</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
       <c r="J173" t="n">
         <v>3</v>
       </c>
-      <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7721,12 +7608,9 @@
           <t>Balibo</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
       <c r="J174" t="n">
         <v>5</v>
       </c>
-      <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7762,12 +7646,9 @@
           <t>Balibo</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
       <c r="J175" t="n">
         <v>7</v>
       </c>
-      <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7803,12 +7684,9 @@
           <t>Balibo</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
       <c r="J176" t="n">
         <v>5</v>
       </c>
-      <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7844,12 +7722,9 @@
           <t>Suai</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
       <c r="J177" t="n">
         <v>5</v>
       </c>
-      <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7885,12 +7760,9 @@
           <t>Suai</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
       <c r="J178" t="n">
         <v>4</v>
       </c>
-      <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7926,12 +7798,9 @@
           <t>Suai</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
       <c r="J179" t="n">
         <v>11</v>
       </c>
-      <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7967,12 +7836,9 @@
           <t>Suai</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
       <c r="J180" t="n">
         <v>9</v>
       </c>
-      <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8008,12 +7874,9 @@
           <t>Suai</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
       <c r="J181" t="n">
         <v>5</v>
       </c>
-      <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8049,12 +7912,9 @@
           <t>Tilomar</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
       <c r="J182" t="n">
         <v>7</v>
       </c>
-      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8090,12 +7950,9 @@
           <t>Tilomar</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
       <c r="J183" t="n">
         <v>7</v>
       </c>
-      <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8131,12 +7988,9 @@
           <t>Tilomar</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
       <c r="J184" t="n">
         <v>6</v>
       </c>
-      <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8172,12 +8026,9 @@
           <t>Tilomar</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
       <c r="J185" t="n">
         <v>3</v>
       </c>
-      <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8213,12 +8064,9 @@
           <t>Fatumean</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
       <c r="J186" t="n">
         <v>4</v>
       </c>
-      <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8254,12 +8102,9 @@
           <t>Fatumean</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
       <c r="J187" t="n">
         <v>4</v>
       </c>
-      <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8295,12 +8140,9 @@
           <t>Fatumean</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
       <c r="J188" t="n">
         <v>4</v>
       </c>
-      <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8336,12 +8178,9 @@
           <t>Fohorem</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
       <c r="J189" t="n">
         <v>5</v>
       </c>
-      <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8377,12 +8216,9 @@
           <t>Fohorem</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
       <c r="J190" t="n">
         <v>3</v>
       </c>
-      <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8418,12 +8254,9 @@
           <t>Fohorem</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
       <c r="J191" t="n">
         <v>4</v>
       </c>
-      <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8459,12 +8292,9 @@
           <t>Fohorem</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
       <c r="J192" t="n">
         <v>3</v>
       </c>
-      <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8500,12 +8330,9 @@
           <t>Maucatar</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
       <c r="J193" t="n">
         <v>4</v>
       </c>
-      <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8541,12 +8368,9 @@
           <t>Maucatar</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
       <c r="J194" t="n">
         <v>7</v>
       </c>
-      <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8582,12 +8406,9 @@
           <t>Maucatar</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
       <c r="J195" t="n">
         <v>5</v>
       </c>
-      <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8623,12 +8444,9 @@
           <t>Maucatar</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
       <c r="J196" t="n">
         <v>6</v>
       </c>
-      <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8664,12 +8482,9 @@
           <t>Zumalai</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
       <c r="J197" t="n">
         <v>4</v>
       </c>
-      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8705,12 +8520,9 @@
           <t>Zumalai</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr"/>
       <c r="J198" t="n">
         <v>3</v>
       </c>
-      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8746,12 +8558,9 @@
           <t>Zumalai</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
       <c r="J199" t="n">
         <v>5</v>
       </c>
-      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8787,12 +8596,9 @@
           <t>Zumalai</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
       <c r="J200" t="n">
         <v>2</v>
       </c>
-      <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8828,12 +8634,9 @@
           <t>Zumalai</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
       <c r="J201" t="n">
         <v>7</v>
       </c>
-      <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8869,12 +8672,9 @@
           <t>Zumalai</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
       <c r="J202" t="n">
         <v>4</v>
       </c>
-      <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8910,12 +8710,9 @@
           <t>Zumalai</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr"/>
-      <c r="I203" t="inlineStr"/>
       <c r="J203" t="n">
         <v>5</v>
       </c>
-      <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8951,12 +8748,9 @@
           <t>Zumalai</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
       <c r="J204" t="n">
         <v>4</v>
       </c>
-      <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8992,12 +8786,9 @@
           <t>Fatululic</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr"/>
       <c r="J205" t="n">
         <v>3</v>
       </c>
-      <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9033,12 +8824,9 @@
           <t>Fatululic</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr"/>
       <c r="J206" t="n">
         <v>5</v>
       </c>
-      <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9074,12 +8862,9 @@
           <t>Vera Cruz</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
       <c r="J207" t="n">
         <v>10</v>
       </c>
-      <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9115,12 +8900,9 @@
           <t>Vera Cruz</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
       <c r="J208" t="n">
         <v>11</v>
       </c>
-      <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -9156,12 +8938,9 @@
           <t>Vera Cruz</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr"/>
-      <c r="I209" t="inlineStr"/>
       <c r="J209" t="n">
         <v>9</v>
       </c>
-      <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9197,12 +8976,9 @@
           <t>Vera Cruz</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
       <c r="J210" t="n">
         <v>6</v>
       </c>
-      <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -9238,12 +9014,9 @@
           <t>Vera Cruz</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
       <c r="J211" t="n">
         <v>5</v>
       </c>
-      <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -9279,12 +9052,9 @@
           <t>Vera Cruz</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
       <c r="J212" t="n">
         <v>2</v>
       </c>
-      <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -9320,12 +9090,9 @@
           <t>Vera Cruz</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr"/>
       <c r="J213" t="n">
         <v>5</v>
       </c>
-      <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -9361,12 +9128,9 @@
           <t>Metinaro</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
       <c r="J214" t="n">
         <v>6</v>
       </c>
-      <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9402,12 +9166,9 @@
           <t>Metinaro</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr"/>
-      <c r="I215" t="inlineStr"/>
       <c r="J215" t="n">
         <v>4</v>
       </c>
-      <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -9443,135 +9204,168 @@
           <t>Metinaro</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
       <c r="J216" t="n">
         <v>4</v>
       </c>
-      <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="4" t="inlineStr">
+      <c r="A217" s="5" t="inlineStr">
         <is>
           <t>DIL</t>
         </is>
       </c>
-      <c r="B217" s="4" t="inlineStr">
+      <c r="B217" s="5" t="inlineStr">
         <is>
           <t>Díli</t>
         </is>
       </c>
-      <c r="C217" s="4" t="n">
+      <c r="C217" s="5" t="n">
         <v>216</v>
       </c>
-      <c r="D217" s="4" t="inlineStr">
+      <c r="D217" s="5" t="inlineStr">
         <is>
           <t>DIL-S216</t>
         </is>
       </c>
-      <c r="E217" s="4" t="inlineStr">
+      <c r="E217" s="5" t="inlineStr">
         <is>
           <t>Akadiru Hun</t>
         </is>
       </c>
-      <c r="F217" s="4" t="inlineStr"/>
-      <c r="G217" s="4" t="inlineStr"/>
-      <c r="H217" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I217" s="4" t="inlineStr">
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>DIL-04</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="inlineStr">
+        <is>
+          <t>Nain Feto</t>
+        </is>
+      </c>
+      <c r="H217" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I217" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: DIL-04 Nain Feto</t>
         </is>
       </c>
-      <c r="J217" s="4" t="n">
+      <c r="J217" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K217" s="4" t="inlineStr"/>
+      <c r="K217" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Nain_Feto_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0605__nain_feto/</t>
+        </is>
+      </c>
     </row>
     <row r="218">
-      <c r="A218" s="4" t="inlineStr">
+      <c r="A218" s="5" t="inlineStr">
         <is>
           <t>DIL</t>
         </is>
       </c>
-      <c r="B218" s="4" t="inlineStr">
+      <c r="B218" s="5" t="inlineStr">
         <is>
           <t>Díli</t>
         </is>
       </c>
-      <c r="C218" s="4" t="n">
+      <c r="C218" s="5" t="n">
         <v>217</v>
       </c>
-      <c r="D218" s="4" t="inlineStr">
+      <c r="D218" s="5" t="inlineStr">
         <is>
           <t>DIL-S217</t>
         </is>
       </c>
-      <c r="E218" s="4" t="inlineStr">
+      <c r="E218" s="5" t="inlineStr">
         <is>
           <t>Bemori</t>
         </is>
       </c>
-      <c r="F218" s="4" t="inlineStr"/>
-      <c r="G218" s="4" t="inlineStr"/>
-      <c r="H218" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I218" s="4" t="inlineStr">
+      <c r="F218" s="5" t="inlineStr">
+        <is>
+          <t>DIL-04</t>
+        </is>
+      </c>
+      <c r="G218" s="5" t="inlineStr">
+        <is>
+          <t>Nain Feto</t>
+        </is>
+      </c>
+      <c r="H218" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I218" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: DIL-04 Nain Feto</t>
         </is>
       </c>
-      <c r="J218" s="4" t="n">
+      <c r="J218" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="K218" s="4" t="inlineStr"/>
+      <c r="K218" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Nain_Feto_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0605__nain_feto/</t>
+        </is>
+      </c>
     </row>
     <row r="219">
-      <c r="A219" s="4" t="inlineStr">
+      <c r="A219" s="5" t="inlineStr">
         <is>
           <t>DIL</t>
         </is>
       </c>
-      <c r="B219" s="4" t="inlineStr">
+      <c r="B219" s="5" t="inlineStr">
         <is>
           <t>Díli</t>
         </is>
       </c>
-      <c r="C219" s="4" t="n">
+      <c r="C219" s="5" t="n">
         <v>218</v>
       </c>
-      <c r="D219" s="4" t="inlineStr">
+      <c r="D219" s="5" t="inlineStr">
         <is>
           <t>DIL-S218</t>
         </is>
       </c>
-      <c r="E219" s="4" t="inlineStr">
+      <c r="E219" s="5" t="inlineStr">
         <is>
           <t>Bidau Licedere</t>
         </is>
       </c>
-      <c r="F219" s="4" t="inlineStr"/>
-      <c r="G219" s="4" t="inlineStr"/>
-      <c r="H219" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I219" s="4" t="inlineStr">
+      <c r="F219" s="5" t="inlineStr">
+        <is>
+          <t>DIL-04</t>
+        </is>
+      </c>
+      <c r="G219" s="5" t="inlineStr">
+        <is>
+          <t>Nain Feto</t>
+        </is>
+      </c>
+      <c r="H219" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I219" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: DIL-04 Nain Feto</t>
         </is>
       </c>
-      <c r="J219" s="4" t="n">
+      <c r="J219" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="K219" s="4" t="inlineStr"/>
+      <c r="K219" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Nain_Feto_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0605__nain_feto/</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9607,12 +9401,9 @@
           <t>Nain Feto</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
       <c r="J220" t="n">
         <v>3</v>
       </c>
-      <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9648,53 +9439,62 @@
           <t>Nain Feto</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr"/>
       <c r="J221" t="n">
         <v>10</v>
       </c>
-      <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="4" t="inlineStr">
+      <c r="A222" s="5" t="inlineStr">
         <is>
           <t>DIL</t>
         </is>
       </c>
-      <c r="B222" s="4" t="inlineStr">
+      <c r="B222" s="5" t="inlineStr">
         <is>
           <t>Díli</t>
         </is>
       </c>
-      <c r="C222" s="4" t="n">
+      <c r="C222" s="5" t="n">
         <v>221</v>
       </c>
-      <c r="D222" s="4" t="inlineStr">
+      <c r="D222" s="5" t="inlineStr">
         <is>
           <t>DIL-S221</t>
         </is>
       </c>
-      <c r="E222" s="4" t="inlineStr">
+      <c r="E222" s="5" t="inlineStr">
         <is>
           <t>Lahane Oriental</t>
         </is>
       </c>
-      <c r="F222" s="4" t="inlineStr"/>
-      <c r="G222" s="4" t="inlineStr"/>
-      <c r="H222" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I222" s="4" t="inlineStr">
+      <c r="F222" s="5" t="inlineStr">
+        <is>
+          <t>DIL-04</t>
+        </is>
+      </c>
+      <c r="G222" s="5" t="inlineStr">
+        <is>
+          <t>Nain Feto</t>
+        </is>
+      </c>
+      <c r="H222" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I222" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: DIL-04 Nain Feto / DIL-01 Cristo Rei</t>
         </is>
       </c>
-      <c r="J222" s="4" t="n">
+      <c r="J222" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="K222" s="4" t="inlineStr"/>
+      <c r="K222" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Nain_Feto_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0605__nain_feto/</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -9730,12 +9530,9 @@
           <t>Cristo Rei</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr"/>
-      <c r="I223" t="inlineStr"/>
       <c r="J223" t="n">
         <v>4</v>
       </c>
-      <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -9771,12 +9568,9 @@
           <t>Cristo Rei</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
       <c r="J224" t="n">
         <v>4</v>
       </c>
-      <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -9812,12 +9606,9 @@
           <t>Cristo Rei</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
       <c r="J225" t="n">
         <v>10</v>
       </c>
-      <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -9853,12 +9644,9 @@
           <t>Cristo Rei</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
       <c r="J226" t="n">
         <v>4</v>
       </c>
-      <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -9894,12 +9682,9 @@
           <t>Cristo Rei</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr"/>
-      <c r="I227" t="inlineStr"/>
       <c r="J227" t="n">
         <v>13</v>
       </c>
-      <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -9935,12 +9720,9 @@
           <t>Cristo Rei</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr"/>
-      <c r="I228" t="inlineStr"/>
       <c r="J228" t="n">
         <v>7</v>
       </c>
-      <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -9976,12 +9758,9 @@
           <t>Cristo Rei</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
       <c r="J229" t="n">
         <v>6</v>
       </c>
-      <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -10017,53 +9796,62 @@
           <t>Cristo Rei</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr"/>
       <c r="J230" t="n">
         <v>3</v>
       </c>
-      <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="4" t="inlineStr">
+      <c r="A231" s="5" t="inlineStr">
         <is>
           <t>DIL</t>
         </is>
       </c>
-      <c r="B231" s="4" t="inlineStr">
+      <c r="B231" s="5" t="inlineStr">
         <is>
           <t>Díli</t>
         </is>
       </c>
-      <c r="C231" s="4" t="n">
+      <c r="C231" s="5" t="n">
         <v>230</v>
       </c>
-      <c r="D231" s="4" t="inlineStr">
+      <c r="D231" s="5" t="inlineStr">
         <is>
           <t>DIL-S230</t>
         </is>
       </c>
-      <c r="E231" s="4" t="inlineStr">
+      <c r="E231" s="5" t="inlineStr">
         <is>
           <t>Madohi</t>
         </is>
       </c>
-      <c r="F231" s="4" t="inlineStr"/>
-      <c r="G231" s="4" t="inlineStr"/>
-      <c r="H231" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I231" s="4" t="inlineStr">
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>DIL-02</t>
+        </is>
+      </c>
+      <c r="G231" s="5" t="inlineStr">
+        <is>
+          <t>Dom Aleixo</t>
+        </is>
+      </c>
+      <c r="H231" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I231" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: DIL-02 Dom Aleixo / DIL-01 Cristo Rei</t>
         </is>
       </c>
-      <c r="J231" s="4" t="n">
+      <c r="J231" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="K231" s="4" t="inlineStr"/>
+      <c r="K231" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Dom_Aleixo_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0603__dom_aleixo/</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -10099,12 +9887,9 @@
           <t>Dom Aleixo</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
       <c r="J232" t="n">
         <v>26</v>
       </c>
-      <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -10140,12 +9925,9 @@
           <t>Dom Aleixo</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr"/>
       <c r="J233" t="n">
         <v>14</v>
       </c>
-      <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -10181,12 +9963,9 @@
           <t>Dom Aleixo</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
       <c r="J234" t="n">
         <v>10</v>
       </c>
-      <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -10222,12 +10001,9 @@
           <t>Dom Aleixo</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
       <c r="J235" t="n">
         <v>5</v>
       </c>
-      <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -10263,12 +10039,9 @@
           <t>Dom Aleixo</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
       <c r="J236" t="n">
         <v>5</v>
       </c>
-      <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -10304,12 +10077,9 @@
           <t>Dom Aleixo</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr"/>
-      <c r="I237" t="inlineStr"/>
       <c r="J237" t="n">
         <v>3</v>
       </c>
-      <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -10345,12 +10115,9 @@
           <t>Ermera</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
       <c r="J238" t="n">
         <v>4</v>
       </c>
-      <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -10386,12 +10153,9 @@
           <t>Ermera</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr"/>
       <c r="J239" t="n">
         <v>4</v>
       </c>
-      <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -10427,12 +10191,9 @@
           <t>Ermera</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr"/>
-      <c r="I240" t="inlineStr"/>
       <c r="J240" t="n">
         <v>5</v>
       </c>
-      <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -10468,12 +10229,9 @@
           <t>Ermera</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr"/>
       <c r="J241" t="n">
         <v>5</v>
       </c>
-      <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -10509,12 +10267,9 @@
           <t>Ermera</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr"/>
       <c r="J242" t="n">
         <v>3</v>
       </c>
-      <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -10550,12 +10305,9 @@
           <t>Ermera</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
       <c r="J243" t="n">
         <v>6</v>
       </c>
-      <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -10591,12 +10343,9 @@
           <t>Ermera</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr"/>
       <c r="J244" t="n">
         <v>6</v>
       </c>
-      <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -10632,12 +10381,9 @@
           <t>Ermera</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr"/>
-      <c r="I245" t="inlineStr"/>
       <c r="J245" t="n">
         <v>12</v>
       </c>
-      <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -10673,12 +10419,9 @@
           <t>Ermera</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr"/>
       <c r="J246" t="n">
         <v>5</v>
       </c>
-      <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -10714,94 +10457,115 @@
           <t>Ermera</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr"/>
-      <c r="I247" t="inlineStr"/>
       <c r="J247" t="n">
         <v>5</v>
       </c>
-      <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="4" t="inlineStr">
+      <c r="A248" s="5" t="inlineStr">
         <is>
           <t>ERM</t>
         </is>
       </c>
-      <c r="B248" s="4" t="inlineStr">
+      <c r="B248" s="5" t="inlineStr">
         <is>
           <t>Ermera</t>
         </is>
       </c>
-      <c r="C248" s="4" t="n">
+      <c r="C248" s="5" t="n">
         <v>247</v>
       </c>
-      <c r="D248" s="4" t="inlineStr">
+      <c r="D248" s="5" t="inlineStr">
         <is>
           <t>ERM-S247</t>
         </is>
       </c>
-      <c r="E248" s="4" t="inlineStr">
+      <c r="E248" s="5" t="inlineStr">
         <is>
           <t>Poetete Lodudu</t>
         </is>
       </c>
-      <c r="F248" s="4" t="inlineStr"/>
-      <c r="G248" s="4" t="inlineStr"/>
-      <c r="H248" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I248" s="4" t="inlineStr">
+      <c r="F248" s="5" t="inlineStr">
+        <is>
+          <t>ERM-02</t>
+        </is>
+      </c>
+      <c r="G248" s="5" t="inlineStr">
+        <is>
+          <t>Ermera</t>
+        </is>
+      </c>
+      <c r="H248" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I248" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: ERM-02 Ermera / ERM-01 Atsabe</t>
         </is>
       </c>
-      <c r="J248" s="4" t="n">
+      <c r="J248" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K248" s="4" t="inlineStr"/>
+      <c r="K248" s="5" t="inlineStr">
+        <is>
+          <t>Fonte web hakerek suco ida "Poetete" (Postu Ermera); Fonte postu: https://en.wikipedia.org/wiki/Ermera_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="249">
-      <c r="A249" s="4" t="inlineStr">
+      <c r="A249" s="5" t="inlineStr">
         <is>
           <t>ERM</t>
         </is>
       </c>
-      <c r="B249" s="4" t="inlineStr">
+      <c r="B249" s="5" t="inlineStr">
         <is>
           <t>Ermera</t>
         </is>
       </c>
-      <c r="C249" s="4" t="n">
+      <c r="C249" s="5" t="n">
         <v>248</v>
       </c>
-      <c r="D249" s="4" t="inlineStr">
+      <c r="D249" s="5" t="inlineStr">
         <is>
           <t>ERM-S248</t>
         </is>
       </c>
-      <c r="E249" s="4" t="inlineStr">
+      <c r="E249" s="5" t="inlineStr">
         <is>
           <t>Poetete Vila</t>
         </is>
       </c>
-      <c r="F249" s="4" t="inlineStr"/>
-      <c r="G249" s="4" t="inlineStr"/>
-      <c r="H249" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I249" s="4" t="inlineStr">
+      <c r="F249" s="5" t="inlineStr">
+        <is>
+          <t>ERM-02</t>
+        </is>
+      </c>
+      <c r="G249" s="5" t="inlineStr">
+        <is>
+          <t>Ermera</t>
+        </is>
+      </c>
+      <c r="H249" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I249" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: ERM-02 Ermera / ERM-01 Atsabe</t>
         </is>
       </c>
-      <c r="J249" s="4" t="n">
+      <c r="J249" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K249" s="4" t="inlineStr"/>
+      <c r="K249" s="5" t="inlineStr">
+        <is>
+          <t>Fonte web hakerek suco ida "Poetete" (Postu Ermera); Fonte postu: https://en.wikipedia.org/wiki/Ermera_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -10837,12 +10601,9 @@
           <t>Atsabe</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr"/>
-      <c r="I250" t="inlineStr"/>
       <c r="J250" t="n">
         <v>6</v>
       </c>
-      <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -10878,12 +10639,9 @@
           <t>Atsabe</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr"/>
-      <c r="I251" t="inlineStr"/>
       <c r="J251" t="n">
         <v>6</v>
       </c>
-      <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -10919,12 +10677,9 @@
           <t>Atsabe</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr"/>
-      <c r="I252" t="inlineStr"/>
       <c r="J252" t="n">
         <v>4</v>
       </c>
-      <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -10960,12 +10715,9 @@
           <t>Atsabe</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr"/>
-      <c r="I253" t="inlineStr"/>
       <c r="J253" t="n">
         <v>4</v>
       </c>
-      <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -11001,12 +10753,9 @@
           <t>Atsabe</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr"/>
-      <c r="I254" t="inlineStr"/>
       <c r="J254" t="n">
         <v>4</v>
       </c>
-      <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -11042,12 +10791,9 @@
           <t>Atsabe</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr"/>
       <c r="J255" t="n">
         <v>4</v>
       </c>
-      <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -11083,12 +10829,9 @@
           <t>Atsabe</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr"/>
-      <c r="I256" t="inlineStr"/>
       <c r="J256" t="n">
         <v>3</v>
       </c>
-      <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -11124,12 +10867,9 @@
           <t>Atsabe</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr"/>
-      <c r="I257" t="inlineStr"/>
       <c r="J257" t="n">
         <v>8</v>
       </c>
-      <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -11165,12 +10905,9 @@
           <t>Atsabe</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr"/>
-      <c r="I258" t="inlineStr"/>
       <c r="J258" t="n">
         <v>4</v>
       </c>
-      <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -11206,12 +10943,9 @@
           <t>Atsabe</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr"/>
-      <c r="I259" t="inlineStr"/>
       <c r="J259" t="n">
         <v>7</v>
       </c>
-      <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -11247,12 +10981,9 @@
           <t>Atsabe</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr"/>
-      <c r="I260" t="inlineStr"/>
       <c r="J260" t="n">
         <v>6</v>
       </c>
-      <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -11288,12 +11019,9 @@
           <t>Atsabe</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr"/>
-      <c r="I261" t="inlineStr"/>
       <c r="J261" t="n">
         <v>3</v>
       </c>
-      <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -11329,12 +11057,9 @@
           <t>Atsabe</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr"/>
-      <c r="I262" t="inlineStr"/>
       <c r="J262" t="n">
         <v>6</v>
       </c>
-      <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -11370,12 +11095,9 @@
           <t>Hatulia A</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr"/>
-      <c r="I263" t="inlineStr"/>
       <c r="J263" t="n">
         <v>4</v>
       </c>
-      <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -11411,12 +11133,9 @@
           <t>Hatulia A</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr"/>
-      <c r="I264" t="inlineStr"/>
       <c r="J264" t="n">
         <v>4</v>
       </c>
-      <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -11452,12 +11171,9 @@
           <t>Hatulia A</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr"/>
-      <c r="I265" t="inlineStr"/>
       <c r="J265" t="n">
         <v>3</v>
       </c>
-      <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -11493,12 +11209,9 @@
           <t>Hatulia A</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr"/>
-      <c r="I266" t="inlineStr"/>
       <c r="J266" t="n">
         <v>4</v>
       </c>
-      <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -11534,12 +11247,9 @@
           <t>Hatulia A</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr"/>
-      <c r="I267" t="inlineStr"/>
       <c r="J267" t="n">
         <v>3</v>
       </c>
-      <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -11575,12 +11285,9 @@
           <t>Hatulia A</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr"/>
-      <c r="I268" t="inlineStr"/>
       <c r="J268" t="n">
         <v>2</v>
       </c>
-      <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -11616,12 +11323,9 @@
           <t>Hatulia A</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr"/>
-      <c r="I269" t="inlineStr"/>
       <c r="J269" t="n">
         <v>5</v>
       </c>
-      <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -11657,12 +11361,9 @@
           <t>Hatulia B</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr"/>
-      <c r="I270" t="inlineStr"/>
       <c r="J270" t="n">
         <v>2</v>
       </c>
-      <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -11698,12 +11399,9 @@
           <t>Hatulia B</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr"/>
-      <c r="I271" t="inlineStr"/>
       <c r="J271" t="n">
         <v>6</v>
       </c>
-      <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -11739,12 +11437,9 @@
           <t>Hatulia B</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr"/>
-      <c r="I272" t="inlineStr"/>
       <c r="J272" t="n">
         <v>4</v>
       </c>
-      <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -11780,12 +11475,9 @@
           <t>Hatulia B</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr"/>
-      <c r="I273" t="inlineStr"/>
       <c r="J273" t="n">
         <v>6</v>
       </c>
-      <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -11821,12 +11513,9 @@
           <t>Hatulia B</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr"/>
-      <c r="I274" t="inlineStr"/>
       <c r="J274" t="n">
         <v>4</v>
       </c>
-      <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -11862,53 +11551,62 @@
           <t>Hatulia B</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr"/>
-      <c r="I275" t="inlineStr"/>
       <c r="J275" t="n">
         <v>6</v>
       </c>
-      <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="4" t="inlineStr">
+      <c r="A276" s="5" t="inlineStr">
         <is>
           <t>ERM</t>
         </is>
       </c>
-      <c r="B276" s="4" t="inlineStr">
+      <c r="B276" s="5" t="inlineStr">
         <is>
           <t>Ermera</t>
         </is>
       </c>
-      <c r="C276" s="4" t="n">
+      <c r="C276" s="5" t="n">
         <v>275</v>
       </c>
-      <c r="D276" s="4" t="inlineStr">
+      <c r="D276" s="5" t="inlineStr">
         <is>
           <t>ERM-S275</t>
         </is>
       </c>
-      <c r="E276" s="4" t="inlineStr">
+      <c r="E276" s="5" t="inlineStr">
         <is>
           <t>Railaco Leten</t>
         </is>
       </c>
-      <c r="F276" s="4" t="inlineStr"/>
-      <c r="G276" s="4" t="inlineStr"/>
-      <c r="H276" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I276" s="4" t="inlineStr">
+      <c r="F276" s="5" t="inlineStr">
+        <is>
+          <t>ERM-05</t>
+        </is>
+      </c>
+      <c r="G276" s="5" t="inlineStr">
+        <is>
+          <t>Railaco</t>
+        </is>
+      </c>
+      <c r="H276" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I276" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: ERM-05 Railaco / ERM-07 Hatulia B</t>
         </is>
       </c>
-      <c r="J276" s="4" t="n">
+      <c r="J276" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K276" s="4" t="inlineStr"/>
+      <c r="K276" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Railaco_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -11944,12 +11642,9 @@
           <t>Railaco</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr"/>
-      <c r="I277" t="inlineStr"/>
       <c r="J277" t="n">
         <v>2</v>
       </c>
-      <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -11985,12 +11680,9 @@
           <t>Railaco</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr"/>
-      <c r="I278" t="inlineStr"/>
       <c r="J278" t="n">
         <v>2</v>
       </c>
-      <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -12026,12 +11718,9 @@
           <t>Railaco</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr"/>
-      <c r="I279" t="inlineStr"/>
       <c r="J279" t="n">
         <v>4</v>
       </c>
-      <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -12067,12 +11756,9 @@
           <t>Railaco</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr"/>
-      <c r="I280" t="inlineStr"/>
       <c r="J280" t="n">
         <v>4</v>
       </c>
-      <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -12108,12 +11794,9 @@
           <t>Railaco</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr"/>
-      <c r="I281" t="inlineStr"/>
       <c r="J281" t="n">
         <v>3</v>
       </c>
-      <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -12149,12 +11832,9 @@
           <t>Railaco</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr"/>
-      <c r="I282" t="inlineStr"/>
       <c r="J282" t="n">
         <v>4</v>
       </c>
-      <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -12190,53 +11870,62 @@
           <t>Railaco</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr"/>
-      <c r="I283" t="inlineStr"/>
       <c r="J283" t="n">
         <v>2</v>
       </c>
-      <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="4" t="inlineStr">
+      <c r="A284" s="5" t="inlineStr">
         <is>
           <t>ERM</t>
         </is>
       </c>
-      <c r="B284" s="4" t="inlineStr">
+      <c r="B284" s="5" t="inlineStr">
         <is>
           <t>Ermera</t>
         </is>
       </c>
-      <c r="C284" s="4" t="n">
+      <c r="C284" s="5" t="n">
         <v>283</v>
       </c>
-      <c r="D284" s="4" t="inlineStr">
+      <c r="D284" s="5" t="inlineStr">
         <is>
           <t>ERM-S283</t>
         </is>
       </c>
-      <c r="E284" s="4" t="inlineStr">
+      <c r="E284" s="5" t="inlineStr">
         <is>
           <t>Tocoluli</t>
         </is>
       </c>
-      <c r="F284" s="4" t="inlineStr"/>
-      <c r="G284" s="4" t="inlineStr"/>
-      <c r="H284" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I284" s="4" t="inlineStr">
+      <c r="F284" s="5" t="inlineStr">
+        <is>
+          <t>ERM-05</t>
+        </is>
+      </c>
+      <c r="G284" s="5" t="inlineStr">
+        <is>
+          <t>Railaco</t>
+        </is>
+      </c>
+      <c r="H284" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I284" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: ERM-05 Railaco / ERM-04 Letefoho</t>
         </is>
       </c>
-      <c r="J284" s="4" t="n">
+      <c r="J284" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K284" s="4" t="inlineStr"/>
+      <c r="K284" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Railaco_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -12272,12 +11961,9 @@
           <t>Letefoho</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr"/>
-      <c r="I285" t="inlineStr"/>
       <c r="J285" t="n">
         <v>5</v>
       </c>
-      <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -12313,12 +11999,9 @@
           <t>Letefoho</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr"/>
-      <c r="I286" t="inlineStr"/>
       <c r="J286" t="n">
         <v>8</v>
       </c>
-      <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -12354,12 +12037,9 @@
           <t>Letefoho</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr"/>
-      <c r="I287" t="inlineStr"/>
       <c r="J287" t="n">
         <v>9</v>
       </c>
-      <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -12395,12 +12075,9 @@
           <t>Letefoho</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr"/>
-      <c r="I288" t="inlineStr"/>
       <c r="J288" t="n">
         <v>7</v>
       </c>
-      <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -12436,12 +12113,9 @@
           <t>Letefoho</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr"/>
-      <c r="I289" t="inlineStr"/>
       <c r="J289" t="n">
         <v>10</v>
       </c>
-      <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -12477,12 +12151,9 @@
           <t>Letefoho</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr"/>
-      <c r="I290" t="inlineStr"/>
       <c r="J290" t="n">
         <v>6</v>
       </c>
-      <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -12518,12 +12189,9 @@
           <t>Letefoho</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr"/>
-      <c r="I291" t="inlineStr"/>
       <c r="J291" t="n">
         <v>4</v>
       </c>
-      <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -12559,12 +12227,9 @@
           <t>Letefoho</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr"/>
-      <c r="I292" t="inlineStr"/>
       <c r="J292" t="n">
         <v>6</v>
       </c>
-      <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -12600,12 +12265,9 @@
           <t>Letefoho</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr"/>
-      <c r="I293" t="inlineStr"/>
       <c r="J293" t="n">
         <v>12</v>
       </c>
-      <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -12641,12 +12303,9 @@
           <t>Iliomar</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr"/>
-      <c r="I294" t="inlineStr"/>
       <c r="J294" t="n">
         <v>4</v>
       </c>
-      <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -12682,12 +12341,9 @@
           <t>Iliomar</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr"/>
-      <c r="I295" t="inlineStr"/>
       <c r="J295" t="n">
         <v>5</v>
       </c>
-      <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -12723,12 +12379,9 @@
           <t>Iliomar</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr"/>
-      <c r="I296" t="inlineStr"/>
       <c r="J296" t="n">
         <v>3</v>
       </c>
-      <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -12764,8 +12417,6 @@
           <t>Iliomar</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr"/>
-      <c r="I297" t="inlineStr"/>
       <c r="J297" t="n">
         <v>5</v>
       </c>
@@ -12809,8 +12460,6 @@
           <t>Iliomar</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr"/>
-      <c r="I298" t="inlineStr"/>
       <c r="J298" t="n">
         <v>5</v>
       </c>
@@ -12854,471 +12503,592 @@
           <t>Iliomar</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr"/>
-      <c r="I299" t="inlineStr"/>
       <c r="J299" t="n">
         <v>3</v>
       </c>
-      <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" s="4" t="inlineStr">
+      <c r="A300" s="5" t="inlineStr">
         <is>
           <t>LAU</t>
         </is>
       </c>
-      <c r="B300" s="4" t="inlineStr">
+      <c r="B300" s="5" t="inlineStr">
         <is>
           <t>Lautém</t>
         </is>
       </c>
-      <c r="C300" s="4" t="n">
+      <c r="C300" s="5" t="n">
         <v>299</v>
       </c>
-      <c r="D300" s="4" t="inlineStr">
+      <c r="D300" s="5" t="inlineStr">
         <is>
           <t>LAU-S299</t>
         </is>
       </c>
-      <c r="E300" s="4" t="inlineStr">
+      <c r="E300" s="5" t="inlineStr">
         <is>
           <t>Baduro</t>
         </is>
       </c>
-      <c r="F300" s="4" t="inlineStr"/>
-      <c r="G300" s="4" t="inlineStr"/>
-      <c r="H300" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I300" s="4" t="inlineStr">
+      <c r="F300" s="5" t="inlineStr">
+        <is>
+          <t>LAU-02</t>
+        </is>
+      </c>
+      <c r="G300" s="5" t="inlineStr">
+        <is>
+          <t>Lautém</t>
+        </is>
+      </c>
+      <c r="H300" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I300" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: LAU-02 Lautém</t>
         </is>
       </c>
-      <c r="J300" s="4" t="n">
+      <c r="J300" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K300" s="4" t="inlineStr"/>
+      <c r="K300" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Laut%C3%A9m_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="301">
-      <c r="A301" s="4" t="inlineStr">
+      <c r="A301" s="5" t="inlineStr">
         <is>
           <t>LAU</t>
         </is>
       </c>
-      <c r="B301" s="4" t="inlineStr">
+      <c r="B301" s="5" t="inlineStr">
         <is>
           <t>Lautém</t>
         </is>
       </c>
-      <c r="C301" s="4" t="n">
+      <c r="C301" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="D301" s="4" t="inlineStr">
+      <c r="D301" s="5" t="inlineStr">
         <is>
           <t>LAU-S300</t>
         </is>
       </c>
-      <c r="E301" s="4" t="inlineStr">
+      <c r="E301" s="5" t="inlineStr">
         <is>
           <t>Com</t>
         </is>
       </c>
-      <c r="F301" s="4" t="inlineStr"/>
-      <c r="G301" s="4" t="inlineStr"/>
-      <c r="H301" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I301" s="4" t="inlineStr">
+      <c r="F301" s="5" t="inlineStr">
+        <is>
+          <t>LAU-02</t>
+        </is>
+      </c>
+      <c r="G301" s="5" t="inlineStr">
+        <is>
+          <t>Lautém</t>
+        </is>
+      </c>
+      <c r="H301" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I301" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: LAU-02 Lautém</t>
         </is>
       </c>
-      <c r="J301" s="4" t="n">
+      <c r="J301" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="K301" s="4" t="inlineStr"/>
+      <c r="K301" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Laut%C3%A9m_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="302">
-      <c r="A302" s="4" t="inlineStr">
+      <c r="A302" s="5" t="inlineStr">
         <is>
           <t>LAU</t>
         </is>
       </c>
-      <c r="B302" s="4" t="inlineStr">
+      <c r="B302" s="5" t="inlineStr">
         <is>
           <t>Lautém</t>
         </is>
       </c>
-      <c r="C302" s="4" t="n">
+      <c r="C302" s="5" t="n">
         <v>301</v>
       </c>
-      <c r="D302" s="4" t="inlineStr">
+      <c r="D302" s="5" t="inlineStr">
         <is>
           <t>LAU-S301</t>
         </is>
       </c>
-      <c r="E302" s="4" t="inlineStr">
+      <c r="E302" s="5" t="inlineStr">
         <is>
           <t>Daudere</t>
         </is>
       </c>
-      <c r="F302" s="4" t="inlineStr"/>
-      <c r="G302" s="4" t="inlineStr"/>
-      <c r="H302" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I302" s="4" t="inlineStr">
+      <c r="F302" s="5" t="inlineStr">
+        <is>
+          <t>LAU-02</t>
+        </is>
+      </c>
+      <c r="G302" s="5" t="inlineStr">
+        <is>
+          <t>Lautém</t>
+        </is>
+      </c>
+      <c r="H302" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I302" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: LAU-02 Lautém</t>
         </is>
       </c>
-      <c r="J302" s="4" t="n">
+      <c r="J302" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="K302" s="4" t="inlineStr"/>
+      <c r="K302" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Laut%C3%A9m_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="303">
-      <c r="A303" s="4" t="inlineStr">
+      <c r="A303" s="5" t="inlineStr">
         <is>
           <t>LAU</t>
         </is>
       </c>
-      <c r="B303" s="4" t="inlineStr">
+      <c r="B303" s="5" t="inlineStr">
         <is>
           <t>Lautém</t>
         </is>
       </c>
-      <c r="C303" s="4" t="n">
+      <c r="C303" s="5" t="n">
         <v>302</v>
       </c>
-      <c r="D303" s="4" t="inlineStr">
+      <c r="D303" s="5" t="inlineStr">
         <is>
           <t>LAU-S302</t>
         </is>
       </c>
-      <c r="E303" s="4" t="inlineStr">
+      <c r="E303" s="5" t="inlineStr">
         <is>
           <t>Euquisi</t>
         </is>
       </c>
-      <c r="F303" s="4" t="inlineStr"/>
-      <c r="G303" s="4" t="inlineStr"/>
-      <c r="H303" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I303" s="4" t="inlineStr">
+      <c r="F303" s="5" t="inlineStr">
+        <is>
+          <t>LAU-02</t>
+        </is>
+      </c>
+      <c r="G303" s="5" t="inlineStr">
+        <is>
+          <t>Lautém</t>
+        </is>
+      </c>
+      <c r="H303" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I303" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: LAU-02 Lautém</t>
         </is>
       </c>
-      <c r="J303" s="4" t="n">
+      <c r="J303" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K303" s="4" t="inlineStr"/>
+      <c r="K303" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Laut%C3%A9m_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="304">
-      <c r="A304" s="4" t="inlineStr">
+      <c r="A304" s="5" t="inlineStr">
         <is>
           <t>LAU</t>
         </is>
       </c>
-      <c r="B304" s="4" t="inlineStr">
+      <c r="B304" s="5" t="inlineStr">
         <is>
           <t>Lautém</t>
         </is>
       </c>
-      <c r="C304" s="4" t="n">
+      <c r="C304" s="5" t="n">
         <v>303</v>
       </c>
-      <c r="D304" s="4" t="inlineStr">
+      <c r="D304" s="5" t="inlineStr">
         <is>
           <t>LAU-S303</t>
         </is>
       </c>
-      <c r="E304" s="4" t="inlineStr">
+      <c r="E304" s="5" t="inlineStr">
         <is>
           <t>Ililai</t>
         </is>
       </c>
-      <c r="F304" s="4" t="inlineStr"/>
-      <c r="G304" s="4" t="inlineStr"/>
-      <c r="H304" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I304" s="4" t="inlineStr">
+      <c r="F304" s="5" t="inlineStr">
+        <is>
+          <t>LAU-02</t>
+        </is>
+      </c>
+      <c r="G304" s="5" t="inlineStr">
+        <is>
+          <t>Lautém</t>
+        </is>
+      </c>
+      <c r="H304" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I304" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: LAU-02 Lautém</t>
         </is>
       </c>
-      <c r="J304" s="4" t="n">
+      <c r="J304" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="K304" s="4" t="inlineStr"/>
+      <c r="K304" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Laut%C3%A9m_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="305">
-      <c r="A305" s="4" t="inlineStr">
+      <c r="A305" s="5" t="inlineStr">
         <is>
           <t>LAU</t>
         </is>
       </c>
-      <c r="B305" s="4" t="inlineStr">
+      <c r="B305" s="5" t="inlineStr">
         <is>
           <t>Lautém</t>
         </is>
       </c>
-      <c r="C305" s="4" t="n">
+      <c r="C305" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="D305" s="4" t="inlineStr">
+      <c r="D305" s="5" t="inlineStr">
         <is>
           <t>LAU-S304</t>
         </is>
       </c>
-      <c r="E305" s="4" t="inlineStr">
+      <c r="E305" s="5" t="inlineStr">
         <is>
           <t>Maina</t>
         </is>
       </c>
-      <c r="F305" s="4" t="inlineStr"/>
-      <c r="G305" s="4" t="inlineStr"/>
-      <c r="H305" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I305" s="4" t="inlineStr">
+      <c r="F305" s="5" t="inlineStr">
+        <is>
+          <t>LAU-02</t>
+        </is>
+      </c>
+      <c r="G305" s="5" t="inlineStr">
+        <is>
+          <t>Lautém</t>
+        </is>
+      </c>
+      <c r="H305" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I305" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: LAU-02 Lautém</t>
         </is>
       </c>
-      <c r="J305" s="4" t="n">
+      <c r="J305" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K305" s="4" t="inlineStr">
-        <is>
-          <t>Naran hanesan ho suco seluk iha munisípiu ne'e (kódigu la hanesan; PDF la hakerek I/II)</t>
+      <c r="K305" s="5" t="inlineStr">
+        <is>
+          <t>Naran hanesan ho suco seluk iha munisípiu ne'e (kódigu la hanesan; PDF la hakerek I/II); Fonte postu: https://en.wikipedia.org/wiki/Laut%C3%A9m_Administrative_Post</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="4" t="inlineStr">
+      <c r="A306" s="5" t="inlineStr">
         <is>
           <t>LAU</t>
         </is>
       </c>
-      <c r="B306" s="4" t="inlineStr">
+      <c r="B306" s="5" t="inlineStr">
         <is>
           <t>Lautém</t>
         </is>
       </c>
-      <c r="C306" s="4" t="n">
+      <c r="C306" s="5" t="n">
         <v>305</v>
       </c>
-      <c r="D306" s="4" t="inlineStr">
+      <c r="D306" s="5" t="inlineStr">
         <is>
           <t>LAU-S305</t>
         </is>
       </c>
-      <c r="E306" s="4" t="inlineStr">
+      <c r="E306" s="5" t="inlineStr">
         <is>
           <t>Maina</t>
         </is>
       </c>
-      <c r="F306" s="4" t="inlineStr"/>
-      <c r="G306" s="4" t="inlineStr"/>
-      <c r="H306" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I306" s="4" t="inlineStr">
+      <c r="F306" s="5" t="inlineStr">
+        <is>
+          <t>LAU-02</t>
+        </is>
+      </c>
+      <c r="G306" s="5" t="inlineStr">
+        <is>
+          <t>Lautém</t>
+        </is>
+      </c>
+      <c r="H306" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I306" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: LAU-02 Lautém</t>
         </is>
       </c>
-      <c r="J306" s="4" t="n">
+      <c r="J306" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K306" s="4" t="inlineStr">
-        <is>
-          <t>Naran hanesan ho suco seluk iha munisípiu ne'e (kódigu la hanesan; PDF la hakerek I/II)</t>
+      <c r="K306" s="5" t="inlineStr">
+        <is>
+          <t>Naran hanesan ho suco seluk iha munisípiu ne'e (kódigu la hanesan; PDF la hakerek I/II); Fonte postu: https://en.wikipedia.org/wiki/Laut%C3%A9m_Administrative_Post</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="4" t="inlineStr">
+      <c r="A307" s="5" t="inlineStr">
         <is>
           <t>LAU</t>
         </is>
       </c>
-      <c r="B307" s="4" t="inlineStr">
+      <c r="B307" s="5" t="inlineStr">
         <is>
           <t>Lautém</t>
         </is>
       </c>
-      <c r="C307" s="4" t="n">
+      <c r="C307" s="5" t="n">
         <v>306</v>
       </c>
-      <c r="D307" s="4" t="inlineStr">
+      <c r="D307" s="5" t="inlineStr">
         <is>
           <t>LAU-S306</t>
         </is>
       </c>
-      <c r="E307" s="4" t="inlineStr">
+      <c r="E307" s="5" t="inlineStr">
         <is>
           <t>Pairara</t>
         </is>
       </c>
-      <c r="F307" s="4" t="inlineStr"/>
-      <c r="G307" s="4" t="inlineStr"/>
-      <c r="H307" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I307" s="4" t="inlineStr">
+      <c r="F307" s="5" t="inlineStr">
+        <is>
+          <t>LAU-02</t>
+        </is>
+      </c>
+      <c r="G307" s="5" t="inlineStr">
+        <is>
+          <t>Lautém</t>
+        </is>
+      </c>
+      <c r="H307" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I307" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: LAU-02 Lautém</t>
         </is>
       </c>
-      <c r="J307" s="4" t="n">
+      <c r="J307" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K307" s="4" t="inlineStr"/>
+      <c r="K307" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Laut%C3%A9m_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="308">
-      <c r="A308" s="4" t="inlineStr">
+      <c r="A308" s="5" t="inlineStr">
         <is>
           <t>LAU</t>
         </is>
       </c>
-      <c r="B308" s="4" t="inlineStr">
+      <c r="B308" s="5" t="inlineStr">
         <is>
           <t>Lautém</t>
         </is>
       </c>
-      <c r="C308" s="4" t="n">
+      <c r="C308" s="5" t="n">
         <v>307</v>
       </c>
-      <c r="D308" s="4" t="inlineStr">
+      <c r="D308" s="5" t="inlineStr">
         <is>
           <t>LAU-S307</t>
         </is>
       </c>
-      <c r="E308" s="4" t="inlineStr">
+      <c r="E308" s="5" t="inlineStr">
         <is>
           <t>Parlamento</t>
         </is>
       </c>
-      <c r="F308" s="4" t="inlineStr"/>
-      <c r="G308" s="4" t="inlineStr"/>
-      <c r="H308" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I308" s="4" t="inlineStr">
+      <c r="F308" s="5" t="inlineStr">
+        <is>
+          <t>LAU-02</t>
+        </is>
+      </c>
+      <c r="G308" s="5" t="inlineStr">
+        <is>
+          <t>Lautém</t>
+        </is>
+      </c>
+      <c r="H308" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I308" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: LAU-02 Lautém</t>
         </is>
       </c>
-      <c r="J308" s="4" t="n">
+      <c r="J308" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K308" s="4" t="inlineStr"/>
+      <c r="K308" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Laut%C3%A9m_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="309">
-      <c r="A309" s="4" t="inlineStr">
+      <c r="A309" s="5" t="inlineStr">
         <is>
           <t>LAU</t>
         </is>
       </c>
-      <c r="B309" s="4" t="inlineStr">
+      <c r="B309" s="5" t="inlineStr">
         <is>
           <t>Lautém</t>
         </is>
       </c>
-      <c r="C309" s="4" t="n">
+      <c r="C309" s="5" t="n">
         <v>308</v>
       </c>
-      <c r="D309" s="4" t="inlineStr">
+      <c r="D309" s="5" t="inlineStr">
         <is>
           <t>LAU-S308</t>
         </is>
       </c>
-      <c r="E309" s="4" t="inlineStr">
+      <c r="E309" s="5" t="inlineStr">
         <is>
           <t>Serelau</t>
         </is>
       </c>
-      <c r="F309" s="4" t="inlineStr"/>
-      <c r="G309" s="4" t="inlineStr"/>
-      <c r="H309" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I309" s="4" t="inlineStr">
+      <c r="F309" s="5" t="inlineStr">
+        <is>
+          <t>LAU-02</t>
+        </is>
+      </c>
+      <c r="G309" s="5" t="inlineStr">
+        <is>
+          <t>Lautém</t>
+        </is>
+      </c>
+      <c r="H309" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I309" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: LAU-02 Lautém</t>
         </is>
       </c>
-      <c r="J309" s="4" t="n">
+      <c r="J309" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K309" s="4" t="inlineStr"/>
+      <c r="K309" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Laut%C3%A9m_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="310">
-      <c r="A310" s="4" t="inlineStr">
+      <c r="A310" s="5" t="inlineStr">
         <is>
           <t>LAU</t>
         </is>
       </c>
-      <c r="B310" s="4" t="inlineStr">
+      <c r="B310" s="5" t="inlineStr">
         <is>
           <t>Lautém</t>
         </is>
       </c>
-      <c r="C310" s="4" t="n">
+      <c r="C310" s="5" t="n">
         <v>309</v>
       </c>
-      <c r="D310" s="4" t="inlineStr">
+      <c r="D310" s="5" t="inlineStr">
         <is>
           <t>LAU-S309</t>
         </is>
       </c>
-      <c r="E310" s="4" t="inlineStr">
+      <c r="E310" s="5" t="inlineStr">
         <is>
           <t>Bauro</t>
         </is>
       </c>
-      <c r="F310" s="4" t="inlineStr"/>
-      <c r="G310" s="4" t="inlineStr"/>
-      <c r="H310" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I310" s="4" t="inlineStr">
+      <c r="F310" s="5" t="inlineStr">
+        <is>
+          <t>LAU-03</t>
+        </is>
+      </c>
+      <c r="G310" s="5" t="inlineStr">
+        <is>
+          <t>Lospalos</t>
+        </is>
+      </c>
+      <c r="H310" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I310" s="5" t="inlineStr">
         <is>
           <t>Label posto la iha PDF. Hili: LAU-02 Lautém (ka LAU-03 Lospalos)</t>
         </is>
       </c>
-      <c r="J310" s="4" t="n">
+      <c r="J310" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K310" s="4" t="inlineStr"/>
+      <c r="K310" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Lospalos_Administrative_Post ; https://www.citypopulation.de/en/timor/admin/0803__lospalos</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -13354,12 +13124,9 @@
           <t>Lospalos</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr"/>
-      <c r="I311" t="inlineStr"/>
       <c r="J311" t="n">
         <v>4</v>
       </c>
-      <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -13395,12 +13162,9 @@
           <t>Lospalos</t>
         </is>
       </c>
-      <c r="H312" t="inlineStr"/>
-      <c r="I312" t="inlineStr"/>
       <c r="J312" t="n">
         <v>11</v>
       </c>
-      <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -13436,12 +13200,9 @@
           <t>Lospalos</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr"/>
-      <c r="I313" t="inlineStr"/>
       <c r="J313" t="n">
         <v>4</v>
       </c>
-      <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -13477,12 +13238,9 @@
           <t>Lospalos</t>
         </is>
       </c>
-      <c r="H314" t="inlineStr"/>
-      <c r="I314" t="inlineStr"/>
       <c r="J314" t="n">
         <v>4</v>
       </c>
-      <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -13518,12 +13276,9 @@
           <t>Lospalos</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr"/>
-      <c r="I315" t="inlineStr"/>
       <c r="J315" t="n">
         <v>5</v>
       </c>
-      <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -13559,12 +13314,9 @@
           <t>Lospalos</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr"/>
-      <c r="I316" t="inlineStr"/>
       <c r="J316" t="n">
         <v>3</v>
       </c>
-      <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -13600,12 +13352,9 @@
           <t>Lospalos</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr"/>
-      <c r="I317" t="inlineStr"/>
       <c r="J317" t="n">
         <v>7</v>
       </c>
-      <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -13641,12 +13390,9 @@
           <t>Loré</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr"/>
       <c r="J318" t="n">
         <v>6</v>
       </c>
-      <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -13682,12 +13428,9 @@
           <t>Loré</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr"/>
-      <c r="I319" t="inlineStr"/>
       <c r="J319" t="n">
         <v>3</v>
       </c>
-      <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -13723,12 +13466,9 @@
           <t>Luro</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr"/>
-      <c r="I320" t="inlineStr"/>
       <c r="J320" t="n">
         <v>2</v>
       </c>
-      <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -13764,12 +13504,9 @@
           <t>Luro</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr"/>
-      <c r="I321" t="inlineStr"/>
       <c r="J321" t="n">
         <v>3</v>
       </c>
-      <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -13805,12 +13542,9 @@
           <t>Luro</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr"/>
-      <c r="I322" t="inlineStr"/>
       <c r="J322" t="n">
         <v>3</v>
       </c>
-      <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -13846,12 +13580,9 @@
           <t>Luro</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr"/>
       <c r="J323" t="n">
         <v>3</v>
       </c>
-      <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -13887,12 +13618,9 @@
           <t>Luro</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr"/>
       <c r="J324" t="n">
         <v>5</v>
       </c>
-      <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -13928,12 +13656,9 @@
           <t>Luro</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr"/>
       <c r="J325" t="n">
         <v>5</v>
       </c>
-      <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -13969,12 +13694,9 @@
           <t>Tutuala</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr"/>
       <c r="J326" t="n">
         <v>3</v>
       </c>
-      <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -14010,12 +13732,9 @@
           <t>Tutuala</t>
         </is>
       </c>
-      <c r="H327" t="inlineStr"/>
-      <c r="I327" t="inlineStr"/>
       <c r="J327" t="n">
         <v>4</v>
       </c>
-      <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -14051,8 +13770,6 @@
           <t>Bazartete</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr"/>
-      <c r="I328" t="inlineStr"/>
       <c r="J328" t="n">
         <v>3</v>
       </c>
@@ -14096,12 +13813,9 @@
           <t>Bazartete</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr"/>
-      <c r="I329" t="inlineStr"/>
       <c r="J329" t="n">
         <v>4</v>
       </c>
-      <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -14137,12 +13851,9 @@
           <t>Bazartete</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr"/>
-      <c r="I330" t="inlineStr"/>
       <c r="J330" t="n">
         <v>4</v>
       </c>
-      <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -14178,12 +13889,9 @@
           <t>Bazartete</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr"/>
-      <c r="I331" t="inlineStr"/>
       <c r="J331" t="n">
         <v>9</v>
       </c>
-      <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -14219,12 +13927,9 @@
           <t>Bazartete</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr"/>
-      <c r="I332" t="inlineStr"/>
       <c r="J332" t="n">
         <v>3</v>
       </c>
-      <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -14260,12 +13965,9 @@
           <t>Bazartete</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr"/>
-      <c r="I333" t="inlineStr"/>
       <c r="J333" t="n">
         <v>3</v>
       </c>
-      <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -14301,12 +14003,9 @@
           <t>Bazartete</t>
         </is>
       </c>
-      <c r="H334" t="inlineStr"/>
-      <c r="I334" t="inlineStr"/>
       <c r="J334" t="n">
         <v>5</v>
       </c>
-      <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -14342,12 +14041,9 @@
           <t>Bazartete</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr"/>
-      <c r="I335" t="inlineStr"/>
       <c r="J335" t="n">
         <v>10</v>
       </c>
-      <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -14383,94 +14079,115 @@
           <t>Bazartete</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr"/>
-      <c r="I336" t="inlineStr"/>
       <c r="J336" t="n">
         <v>4</v>
       </c>
-      <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
-      <c r="A337" s="4" t="inlineStr">
+      <c r="A337" s="5" t="inlineStr">
         <is>
           <t>LIQ</t>
         </is>
       </c>
-      <c r="B337" s="4" t="inlineStr">
+      <c r="B337" s="5" t="inlineStr">
         <is>
           <t>Liquiçá</t>
         </is>
       </c>
-      <c r="C337" s="4" t="n">
+      <c r="C337" s="5" t="n">
         <v>336</v>
       </c>
-      <c r="D337" s="4" t="inlineStr">
+      <c r="D337" s="5" t="inlineStr">
         <is>
           <t>LIQ-S336</t>
         </is>
       </c>
-      <c r="E337" s="4" t="inlineStr">
+      <c r="E337" s="5" t="inlineStr">
         <is>
           <t>Fahilebu</t>
         </is>
       </c>
-      <c r="F337" s="4" t="inlineStr"/>
-      <c r="G337" s="4" t="inlineStr"/>
-      <c r="H337" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I337" s="4" t="inlineStr">
+      <c r="F337" s="5" t="inlineStr">
+        <is>
+          <t>LIQ-01</t>
+        </is>
+      </c>
+      <c r="G337" s="5" t="inlineStr">
+        <is>
+          <t>Bazartete</t>
+        </is>
+      </c>
+      <c r="H337" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I337" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: LIQ-02 Liquiçá / LIQ-01 Bazartete</t>
         </is>
       </c>
-      <c r="J337" s="4" t="n">
+      <c r="J337" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K337" s="4" t="inlineStr"/>
+      <c r="K337" s="5" t="inlineStr">
+        <is>
+          <t>Fonte web hakerek "Fahilebo"; Fonte postu: https://en.wikipedia.org/wiki/Bazartete_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="338">
-      <c r="A338" s="4" t="inlineStr">
+      <c r="A338" s="5" t="inlineStr">
         <is>
           <t>LIQ</t>
         </is>
       </c>
-      <c r="B338" s="4" t="inlineStr">
+      <c r="B338" s="5" t="inlineStr">
         <is>
           <t>Liquiçá</t>
         </is>
       </c>
-      <c r="C338" s="4" t="n">
+      <c r="C338" s="5" t="n">
         <v>337</v>
       </c>
-      <c r="D338" s="4" t="inlineStr">
+      <c r="D338" s="5" t="inlineStr">
         <is>
           <t>LIQ-S337</t>
         </is>
       </c>
-      <c r="E338" s="4" t="inlineStr">
+      <c r="E338" s="5" t="inlineStr">
         <is>
           <t>Açumanu</t>
         </is>
       </c>
-      <c r="F338" s="4" t="inlineStr"/>
-      <c r="G338" s="4" t="inlineStr"/>
-      <c r="H338" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I338" s="4" t="inlineStr">
+      <c r="F338" s="5" t="inlineStr">
+        <is>
+          <t>LIQ-02</t>
+        </is>
+      </c>
+      <c r="G338" s="5" t="inlineStr">
+        <is>
+          <t>Liquiçá</t>
+        </is>
+      </c>
+      <c r="H338" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I338" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: LIQ-02 Liquiçá / LIQ-01 Bazartete</t>
         </is>
       </c>
-      <c r="J338" s="4" t="n">
+      <c r="J338" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K338" s="4" t="inlineStr"/>
+      <c r="K338" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Liqui%C3%A7%C3%A1_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -14506,12 +14223,9 @@
           <t>Liquiçá</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr"/>
-      <c r="I339" t="inlineStr"/>
       <c r="J339" t="n">
         <v>4</v>
       </c>
-      <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -14547,12 +14261,9 @@
           <t>Liquiçá</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr"/>
-      <c r="I340" t="inlineStr"/>
       <c r="J340" t="n">
         <v>10</v>
       </c>
-      <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -14588,12 +14299,9 @@
           <t>Liquiçá</t>
         </is>
       </c>
-      <c r="H341" t="inlineStr"/>
-      <c r="I341" t="inlineStr"/>
       <c r="J341" t="n">
         <v>4</v>
       </c>
-      <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -14629,12 +14337,9 @@
           <t>Liquiçá</t>
         </is>
       </c>
-      <c r="H342" t="inlineStr"/>
-      <c r="I342" t="inlineStr"/>
       <c r="J342" t="n">
         <v>8</v>
       </c>
-      <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -14670,12 +14375,9 @@
           <t>Liquiçá</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr"/>
-      <c r="I343" t="inlineStr"/>
       <c r="J343" t="n">
         <v>4</v>
       </c>
-      <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -14711,12 +14413,9 @@
           <t>Liquiçá</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr"/>
       <c r="J344" t="n">
         <v>5</v>
       </c>
-      <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -14752,8 +14451,6 @@
           <t>Maubara</t>
         </is>
       </c>
-      <c r="H345" t="inlineStr"/>
-      <c r="I345" t="inlineStr"/>
       <c r="J345" t="n">
         <v>5</v>
       </c>
@@ -14797,12 +14494,9 @@
           <t>Maubara</t>
         </is>
       </c>
-      <c r="H346" t="inlineStr"/>
-      <c r="I346" t="inlineStr"/>
       <c r="J346" t="n">
         <v>10</v>
       </c>
-      <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -14838,12 +14532,9 @@
           <t>Maubara</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr"/>
-      <c r="I347" t="inlineStr"/>
       <c r="J347" t="n">
         <v>7</v>
       </c>
-      <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -14879,12 +14570,9 @@
           <t>Maubara</t>
         </is>
       </c>
-      <c r="H348" t="inlineStr"/>
-      <c r="I348" t="inlineStr"/>
       <c r="J348" t="n">
         <v>11</v>
       </c>
-      <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -14920,12 +14608,9 @@
           <t>Loes</t>
         </is>
       </c>
-      <c r="H349" t="inlineStr"/>
-      <c r="I349" t="inlineStr"/>
       <c r="J349" t="n">
         <v>5</v>
       </c>
-      <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -14961,12 +14646,9 @@
           <t>Loes</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr"/>
-      <c r="I350" t="inlineStr"/>
       <c r="J350" t="n">
         <v>7</v>
       </c>
-      <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -15002,12 +14684,9 @@
           <t>Loes</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr"/>
-      <c r="I351" t="inlineStr"/>
       <c r="J351" t="n">
         <v>5</v>
       </c>
-      <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -15043,12 +14722,9 @@
           <t>Manatuto</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr"/>
-      <c r="I352" t="inlineStr"/>
       <c r="J352" t="n">
         <v>2</v>
       </c>
-      <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -15084,12 +14760,9 @@
           <t>Manatuto</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr"/>
-      <c r="I353" t="inlineStr"/>
       <c r="J353" t="n">
         <v>3</v>
       </c>
-      <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -15125,12 +14798,9 @@
           <t>Manatuto</t>
         </is>
       </c>
-      <c r="H354" t="inlineStr"/>
-      <c r="I354" t="inlineStr"/>
       <c r="J354" t="n">
         <v>5</v>
       </c>
-      <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -15166,12 +14836,9 @@
           <t>Manatuto</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr"/>
-      <c r="I355" t="inlineStr"/>
       <c r="J355" t="n">
         <v>2</v>
       </c>
-      <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -15207,12 +14874,9 @@
           <t>Manatuto</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr"/>
-      <c r="I356" t="inlineStr"/>
       <c r="J356" t="n">
         <v>2</v>
       </c>
-      <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -15248,8 +14912,6 @@
           <t>Manatuto</t>
         </is>
       </c>
-      <c r="H357" t="inlineStr"/>
-      <c r="I357" t="inlineStr"/>
       <c r="J357" t="n">
         <v>3</v>
       </c>
@@ -15293,12 +14955,9 @@
           <t>Manatuto</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr"/>
-      <c r="I358" t="inlineStr"/>
       <c r="J358" t="n">
         <v>2</v>
       </c>
-      <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -15334,12 +14993,9 @@
           <t>Laleia</t>
         </is>
       </c>
-      <c r="H359" t="inlineStr"/>
-      <c r="I359" t="inlineStr"/>
       <c r="J359" t="n">
         <v>7</v>
       </c>
-      <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -15375,12 +15031,9 @@
           <t>Laleia</t>
         </is>
       </c>
-      <c r="H360" t="inlineStr"/>
-      <c r="I360" t="inlineStr"/>
       <c r="J360" t="n">
         <v>3</v>
       </c>
-      <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -15416,12 +15069,9 @@
           <t>Laleia</t>
         </is>
       </c>
-      <c r="H361" t="inlineStr"/>
-      <c r="I361" t="inlineStr"/>
       <c r="J361" t="n">
         <v>3</v>
       </c>
-      <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -15457,12 +15107,9 @@
           <t>Laclo</t>
         </is>
       </c>
-      <c r="H362" t="inlineStr"/>
-      <c r="I362" t="inlineStr"/>
       <c r="J362" t="n">
         <v>4</v>
       </c>
-      <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -15498,12 +15145,9 @@
           <t>Laclo</t>
         </is>
       </c>
-      <c r="H363" t="inlineStr"/>
-      <c r="I363" t="inlineStr"/>
       <c r="J363" t="n">
         <v>5</v>
       </c>
-      <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -15539,12 +15183,9 @@
           <t>Laclo</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr"/>
-      <c r="I364" t="inlineStr"/>
       <c r="J364" t="n">
         <v>4</v>
       </c>
-      <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -15580,53 +15221,62 @@
           <t>Laclo</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr"/>
-      <c r="I365" t="inlineStr"/>
       <c r="J365" t="n">
         <v>4</v>
       </c>
-      <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
-      <c r="A366" s="4" t="inlineStr">
+      <c r="A366" s="5" t="inlineStr">
         <is>
           <t>MAN</t>
         </is>
       </c>
-      <c r="B366" s="4" t="inlineStr">
+      <c r="B366" s="5" t="inlineStr">
         <is>
           <t>Manatuto</t>
         </is>
       </c>
-      <c r="C366" s="4" t="n">
+      <c r="C366" s="5" t="n">
         <v>365</v>
       </c>
-      <c r="D366" s="4" t="inlineStr">
+      <c r="D366" s="5" t="inlineStr">
         <is>
           <t>MAN-S365</t>
         </is>
       </c>
-      <c r="E366" s="4" t="inlineStr">
+      <c r="E366" s="5" t="inlineStr">
         <is>
           <t>Uma Naruc</t>
         </is>
       </c>
-      <c r="F366" s="4" t="inlineStr"/>
-      <c r="G366" s="4" t="inlineStr"/>
-      <c r="H366" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I366" s="4" t="inlineStr">
+      <c r="F366" s="5" t="inlineStr">
+        <is>
+          <t>MAN-02</t>
+        </is>
+      </c>
+      <c r="G366" s="5" t="inlineStr">
+        <is>
+          <t>Laclo</t>
+        </is>
+      </c>
+      <c r="H366" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I366" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: MAN-02 Laclo / MAN-03 Laclubar</t>
         </is>
       </c>
-      <c r="J366" s="4" t="n">
+      <c r="J366" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K366" s="4" t="inlineStr"/>
+      <c r="K366" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://citypopulation.de/en/timor/admin/laclo/100205__uma_naruc/</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -15662,12 +15312,9 @@
           <t>Laclubar</t>
         </is>
       </c>
-      <c r="H367" t="inlineStr"/>
-      <c r="I367" t="inlineStr"/>
       <c r="J367" t="n">
         <v>4</v>
       </c>
-      <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -15703,12 +15350,9 @@
           <t>Laclubar</t>
         </is>
       </c>
-      <c r="H368" t="inlineStr"/>
-      <c r="I368" t="inlineStr"/>
       <c r="J368" t="n">
         <v>4</v>
       </c>
-      <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -15744,12 +15388,9 @@
           <t>Laclubar</t>
         </is>
       </c>
-      <c r="H369" t="inlineStr"/>
-      <c r="I369" t="inlineStr"/>
       <c r="J369" t="n">
         <v>3</v>
       </c>
-      <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -15785,12 +15426,9 @@
           <t>Laclubar</t>
         </is>
       </c>
-      <c r="H370" t="inlineStr"/>
-      <c r="I370" t="inlineStr"/>
       <c r="J370" t="n">
         <v>6</v>
       </c>
-      <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -15826,12 +15464,9 @@
           <t>Laclubar</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr"/>
-      <c r="I371" t="inlineStr"/>
       <c r="J371" t="n">
         <v>8</v>
       </c>
-      <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -15867,53 +15502,62 @@
           <t>Laclubar</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr"/>
-      <c r="I372" t="inlineStr"/>
       <c r="J372" t="n">
         <v>4</v>
       </c>
-      <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
-      <c r="A373" s="4" t="inlineStr">
+      <c r="A373" s="5" t="inlineStr">
         <is>
           <t>MAN</t>
         </is>
       </c>
-      <c r="B373" s="4" t="inlineStr">
+      <c r="B373" s="5" t="inlineStr">
         <is>
           <t>Manatuto</t>
         </is>
       </c>
-      <c r="C373" s="4" t="n">
+      <c r="C373" s="5" t="n">
         <v>372</v>
       </c>
-      <c r="D373" s="4" t="inlineStr">
+      <c r="D373" s="5" t="inlineStr">
         <is>
           <t>MAN-S372</t>
         </is>
       </c>
-      <c r="E373" s="4" t="inlineStr">
+      <c r="E373" s="5" t="inlineStr">
         <is>
           <t>Fatu-Maquerec</t>
         </is>
       </c>
-      <c r="F373" s="4" t="inlineStr"/>
-      <c r="G373" s="4" t="inlineStr"/>
-      <c r="H373" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I373" s="4" t="inlineStr">
+      <c r="F373" s="5" t="inlineStr">
+        <is>
+          <t>MAN-06</t>
+        </is>
+      </c>
+      <c r="G373" s="5" t="inlineStr">
+        <is>
+          <t>Soibada</t>
+        </is>
+      </c>
+      <c r="H373" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I373" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: MAN-06 Soibada / MAN-03 Laclubar</t>
         </is>
       </c>
-      <c r="J373" s="4" t="n">
+      <c r="J373" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="K373" s="4" t="inlineStr"/>
+      <c r="K373" s="5" t="inlineStr">
+        <is>
+          <t>Aldeia Lesuata no Sasahi hanesan ho fonte; Fonte postu: https://de.wikipedia.org/wiki/Fatumaquerec_(Soibada)</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -15949,12 +15593,9 @@
           <t>Soibada</t>
         </is>
       </c>
-      <c r="H374" t="inlineStr"/>
-      <c r="I374" t="inlineStr"/>
       <c r="J374" t="n">
         <v>2</v>
       </c>
-      <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -15990,12 +15631,9 @@
           <t>Soibada</t>
         </is>
       </c>
-      <c r="H375" t="inlineStr"/>
-      <c r="I375" t="inlineStr"/>
       <c r="J375" t="n">
         <v>2</v>
       </c>
-      <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -16031,12 +15669,9 @@
           <t>Soibada</t>
         </is>
       </c>
-      <c r="H376" t="inlineStr"/>
-      <c r="I376" t="inlineStr"/>
       <c r="J376" t="n">
         <v>2</v>
       </c>
-      <c r="K376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -16072,12 +15707,9 @@
           <t>Soibada</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr"/>
-      <c r="I377" t="inlineStr"/>
       <c r="J377" t="n">
         <v>2</v>
       </c>
-      <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -16113,12 +15745,9 @@
           <t>Barique</t>
         </is>
       </c>
-      <c r="H378" t="inlineStr"/>
-      <c r="I378" t="inlineStr"/>
       <c r="J378" t="n">
         <v>2</v>
       </c>
-      <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -16154,12 +15783,9 @@
           <t>Barique</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr"/>
-      <c r="I379" t="inlineStr"/>
       <c r="J379" t="n">
         <v>2</v>
       </c>
-      <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -16195,12 +15821,9 @@
           <t>Barique</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr"/>
-      <c r="I380" t="inlineStr"/>
       <c r="J380" t="n">
         <v>2</v>
       </c>
-      <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -16236,12 +15859,9 @@
           <t>Barique</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr"/>
-      <c r="I381" t="inlineStr"/>
       <c r="J381" t="n">
         <v>3</v>
       </c>
-      <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -16277,12 +15897,9 @@
           <t>Barique</t>
         </is>
       </c>
-      <c r="H382" t="inlineStr"/>
-      <c r="I382" t="inlineStr"/>
       <c r="J382" t="n">
         <v>2</v>
       </c>
-      <c r="K382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -16318,12 +15935,9 @@
           <t>Barique</t>
         </is>
       </c>
-      <c r="H383" t="inlineStr"/>
-      <c r="I383" t="inlineStr"/>
       <c r="J383" t="n">
         <v>2</v>
       </c>
-      <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -16359,12 +15973,9 @@
           <t>Same</t>
         </is>
       </c>
-      <c r="H384" t="inlineStr"/>
-      <c r="I384" t="inlineStr"/>
       <c r="J384" t="n">
         <v>8</v>
       </c>
-      <c r="K384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -16400,12 +16011,9 @@
           <t>Same</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr"/>
-      <c r="I385" t="inlineStr"/>
       <c r="J385" t="n">
         <v>6</v>
       </c>
-      <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -16441,12 +16049,9 @@
           <t>Same</t>
         </is>
       </c>
-      <c r="H386" t="inlineStr"/>
-      <c r="I386" t="inlineStr"/>
       <c r="J386" t="n">
         <v>5</v>
       </c>
-      <c r="K386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -16482,8 +16087,6 @@
           <t>Same</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr"/>
-      <c r="I387" t="inlineStr"/>
       <c r="J387" t="n">
         <v>2</v>
       </c>
@@ -16527,12 +16130,9 @@
           <t>Same</t>
         </is>
       </c>
-      <c r="H388" t="inlineStr"/>
-      <c r="I388" t="inlineStr"/>
       <c r="J388" t="n">
         <v>3</v>
       </c>
-      <c r="K388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -16568,12 +16168,9 @@
           <t>Same</t>
         </is>
       </c>
-      <c r="H389" t="inlineStr"/>
-      <c r="I389" t="inlineStr"/>
       <c r="J389" t="n">
         <v>11</v>
       </c>
-      <c r="K389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -16609,12 +16206,9 @@
           <t>Same</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr"/>
-      <c r="I390" t="inlineStr"/>
       <c r="J390" t="n">
         <v>7</v>
       </c>
-      <c r="K390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -16650,12 +16244,9 @@
           <t>Same</t>
         </is>
       </c>
-      <c r="H391" t="inlineStr"/>
-      <c r="I391" t="inlineStr"/>
       <c r="J391" t="n">
         <v>5</v>
       </c>
-      <c r="K391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -16691,55 +16282,60 @@
           <t>Same</t>
         </is>
       </c>
-      <c r="H392" t="inlineStr"/>
-      <c r="I392" t="inlineStr"/>
       <c r="J392" t="n">
         <v>7</v>
       </c>
-      <c r="K392" t="inlineStr"/>
     </row>
     <row r="393">
-      <c r="A393" s="4" t="inlineStr">
+      <c r="A393" s="5" t="inlineStr">
         <is>
           <t>MNF</t>
         </is>
       </c>
-      <c r="B393" s="4" t="inlineStr">
+      <c r="B393" s="5" t="inlineStr">
         <is>
           <t>Manufahi</t>
         </is>
       </c>
-      <c r="C393" s="4" t="n">
+      <c r="C393" s="5" t="n">
         <v>392</v>
       </c>
-      <c r="D393" s="4" t="inlineStr">
+      <c r="D393" s="5" t="inlineStr">
         <is>
           <t>MNF-S392</t>
         </is>
       </c>
-      <c r="E393" s="4" t="inlineStr">
+      <c r="E393" s="5" t="inlineStr">
         <is>
           <t>Uetano Fatuk-Kuak</t>
         </is>
       </c>
-      <c r="F393" s="4" t="inlineStr"/>
-      <c r="G393" s="4" t="inlineStr"/>
-      <c r="H393" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I393" s="4" t="inlineStr">
+      <c r="F393" s="5" t="inlineStr">
+        <is>
+          <t>MNF-03</t>
+        </is>
+      </c>
+      <c r="G393" s="5" t="inlineStr">
+        <is>
+          <t>Same</t>
+        </is>
+      </c>
+      <c r="H393" s="5" t="inlineStr">
+        <is>
+          <t>DIPLOMA</t>
+        </is>
+      </c>
+      <c r="I393" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: MNF-03 Same / MNF-02 Fatuberlio</t>
         </is>
       </c>
-      <c r="J393" s="4" t="n">
+      <c r="J393" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K393" s="4" t="inlineStr">
-        <is>
-          <t>Novo Suco</t>
+      <c r="K393" s="5" t="inlineStr">
+        <is>
+          <t>Novo Suco; La hetan fonte web (suco foun). Postu tuir orden alfabétiku iha anexu diploma: Same (Babulo…Tutuluro, Uetano) — Fatuberlio hahú ho Bubususo; Fonte postu: Diploma Ministerial 31/2026 (orden anexu)</t>
         </is>
       </c>
     </row>
@@ -16777,12 +16373,9 @@
           <t>Fatuberlio</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr"/>
-      <c r="I394" t="inlineStr"/>
       <c r="J394" t="n">
         <v>5</v>
       </c>
-      <c r="K394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -16818,12 +16411,9 @@
           <t>Fatuberlio</t>
         </is>
       </c>
-      <c r="H395" t="inlineStr"/>
-      <c r="I395" t="inlineStr"/>
       <c r="J395" t="n">
         <v>4</v>
       </c>
-      <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -16859,12 +16449,9 @@
           <t>Fatuberlio</t>
         </is>
       </c>
-      <c r="H396" t="inlineStr"/>
-      <c r="I396" t="inlineStr"/>
       <c r="J396" t="n">
         <v>5</v>
       </c>
-      <c r="K396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -16900,12 +16487,9 @@
           <t>Fatuberlio</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr"/>
-      <c r="I397" t="inlineStr"/>
       <c r="J397" t="n">
         <v>4</v>
       </c>
-      <c r="K397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -16941,53 +16525,62 @@
           <t>Fatuberlio</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr"/>
-      <c r="I398" t="inlineStr"/>
       <c r="J398" t="n">
         <v>5</v>
       </c>
-      <c r="K398" t="inlineStr"/>
     </row>
     <row r="399">
-      <c r="A399" s="4" t="inlineStr">
+      <c r="A399" s="5" t="inlineStr">
         <is>
           <t>MNF</t>
         </is>
       </c>
-      <c r="B399" s="4" t="inlineStr">
+      <c r="B399" s="5" t="inlineStr">
         <is>
           <t>Manufahi</t>
         </is>
       </c>
-      <c r="C399" s="4" t="n">
+      <c r="C399" s="5" t="n">
         <v>398</v>
       </c>
-      <c r="D399" s="4" t="inlineStr">
+      <c r="D399" s="5" t="inlineStr">
         <is>
           <t>MNF-S398</t>
         </is>
       </c>
-      <c r="E399" s="4" t="inlineStr">
+      <c r="E399" s="5" t="inlineStr">
         <is>
           <t>Aitemua</t>
         </is>
       </c>
-      <c r="F399" s="4" t="inlineStr"/>
-      <c r="G399" s="4" t="inlineStr"/>
-      <c r="H399" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I399" s="4" t="inlineStr">
+      <c r="F399" s="5" t="inlineStr">
+        <is>
+          <t>MNF-04</t>
+        </is>
+      </c>
+      <c r="G399" s="5" t="inlineStr">
+        <is>
+          <t>Turiscai</t>
+        </is>
+      </c>
+      <c r="H399" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I399" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: MNF-04 Turiscai / MNF-02 Fatuberlio</t>
         </is>
       </c>
-      <c r="J399" s="4" t="n">
+      <c r="J399" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="K399" s="4" t="inlineStr"/>
+      <c r="K399" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Turiscai_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -17023,12 +16616,9 @@
           <t>Turiscai</t>
         </is>
       </c>
-      <c r="H400" t="inlineStr"/>
-      <c r="I400" t="inlineStr"/>
       <c r="J400" t="n">
         <v>3</v>
       </c>
-      <c r="K400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -17064,12 +16654,9 @@
           <t>Turiscai</t>
         </is>
       </c>
-      <c r="H401" t="inlineStr"/>
-      <c r="I401" t="inlineStr"/>
       <c r="J401" t="n">
         <v>5</v>
       </c>
-      <c r="K401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -17105,12 +16692,9 @@
           <t>Turiscai</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr"/>
-      <c r="I402" t="inlineStr"/>
       <c r="J402" t="n">
         <v>2</v>
       </c>
-      <c r="K402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -17146,12 +16730,9 @@
           <t>Turiscai</t>
         </is>
       </c>
-      <c r="H403" t="inlineStr"/>
-      <c r="I403" t="inlineStr"/>
       <c r="J403" t="n">
         <v>3</v>
       </c>
-      <c r="K403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -17187,12 +16768,9 @@
           <t>Turiscai</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr"/>
-      <c r="I404" t="inlineStr"/>
       <c r="J404" t="n">
         <v>4</v>
       </c>
-      <c r="K404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -17228,12 +16806,9 @@
           <t>Turiscai</t>
         </is>
       </c>
-      <c r="H405" t="inlineStr"/>
-      <c r="I405" t="inlineStr"/>
       <c r="J405" t="n">
         <v>6</v>
       </c>
-      <c r="K405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -17269,12 +16844,9 @@
           <t>Turiscai</t>
         </is>
       </c>
-      <c r="H406" t="inlineStr"/>
-      <c r="I406" t="inlineStr"/>
       <c r="J406" t="n">
         <v>4</v>
       </c>
-      <c r="K406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -17310,12 +16882,9 @@
           <t>Turiscai</t>
         </is>
       </c>
-      <c r="H407" t="inlineStr"/>
-      <c r="I407" t="inlineStr"/>
       <c r="J407" t="n">
         <v>4</v>
       </c>
-      <c r="K407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -17351,53 +16920,62 @@
           <t>Turiscai</t>
         </is>
       </c>
-      <c r="H408" t="inlineStr"/>
-      <c r="I408" t="inlineStr"/>
       <c r="J408" t="n">
         <v>4</v>
       </c>
-      <c r="K408" t="inlineStr"/>
     </row>
     <row r="409">
-      <c r="A409" s="4" t="inlineStr">
+      <c r="A409" s="5" t="inlineStr">
         <is>
           <t>MNF</t>
         </is>
       </c>
-      <c r="B409" s="4" t="inlineStr">
+      <c r="B409" s="5" t="inlineStr">
         <is>
           <t>Manufahi</t>
         </is>
       </c>
-      <c r="C409" s="4" t="n">
+      <c r="C409" s="5" t="n">
         <v>408</v>
       </c>
-      <c r="D409" s="4" t="inlineStr">
+      <c r="D409" s="5" t="inlineStr">
         <is>
           <t>MNF-S408</t>
         </is>
       </c>
-      <c r="E409" s="4" t="inlineStr">
+      <c r="E409" s="5" t="inlineStr">
         <is>
           <t>Orana</t>
         </is>
       </c>
-      <c r="F409" s="4" t="inlineStr"/>
-      <c r="G409" s="4" t="inlineStr"/>
-      <c r="H409" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I409" s="4" t="inlineStr">
+      <c r="F409" s="5" t="inlineStr">
+        <is>
+          <t>MNF-04</t>
+        </is>
+      </c>
+      <c r="G409" s="5" t="inlineStr">
+        <is>
+          <t>Turiscai</t>
+        </is>
+      </c>
+      <c r="H409" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I409" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: MNF-04 Turiscai / MNF-01 Alas</t>
         </is>
       </c>
-      <c r="J409" s="4" t="n">
+      <c r="J409" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="K409" s="4" t="inlineStr"/>
+      <c r="K409" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://en.wikipedia.org/wiki/Turiscai_Administrative_Post</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -17433,12 +17011,9 @@
           <t>Alas</t>
         </is>
       </c>
-      <c r="H410" t="inlineStr"/>
-      <c r="I410" t="inlineStr"/>
       <c r="J410" t="n">
         <v>2</v>
       </c>
-      <c r="K410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -17474,12 +17049,9 @@
           <t>Alas</t>
         </is>
       </c>
-      <c r="H411" t="inlineStr"/>
-      <c r="I411" t="inlineStr"/>
       <c r="J411" t="n">
         <v>3</v>
       </c>
-      <c r="K411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -17515,12 +17087,9 @@
           <t>Alas</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr"/>
-      <c r="I412" t="inlineStr"/>
       <c r="J412" t="n">
         <v>4</v>
       </c>
-      <c r="K412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -17556,12 +17125,9 @@
           <t>Alas</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr"/>
-      <c r="I413" t="inlineStr"/>
       <c r="J413" t="n">
         <v>3</v>
       </c>
-      <c r="K413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -17597,12 +17163,9 @@
           <t>Alas</t>
         </is>
       </c>
-      <c r="H414" t="inlineStr"/>
-      <c r="I414" t="inlineStr"/>
       <c r="J414" t="n">
         <v>5</v>
       </c>
-      <c r="K414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -17638,12 +17201,9 @@
           <t>Alas</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr"/>
-      <c r="I415" t="inlineStr"/>
       <c r="J415" t="n">
         <v>4</v>
       </c>
-      <c r="K415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -17679,12 +17239,9 @@
           <t>Pante Macassar</t>
         </is>
       </c>
-      <c r="H416" t="inlineStr"/>
-      <c r="I416" t="inlineStr"/>
       <c r="J416" t="n">
         <v>2</v>
       </c>
-      <c r="K416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -17720,12 +17277,9 @@
           <t>Pante Macassar</t>
         </is>
       </c>
-      <c r="H417" t="inlineStr"/>
-      <c r="I417" t="inlineStr"/>
       <c r="J417" t="n">
         <v>2</v>
       </c>
-      <c r="K417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -17761,12 +17315,9 @@
           <t>Pante Macassar</t>
         </is>
       </c>
-      <c r="H418" t="inlineStr"/>
-      <c r="I418" t="inlineStr"/>
       <c r="J418" t="n">
         <v>2</v>
       </c>
-      <c r="K418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -17802,12 +17353,9 @@
           <t>Pante Macassar</t>
         </is>
       </c>
-      <c r="H419" t="inlineStr"/>
-      <c r="I419" t="inlineStr"/>
       <c r="J419" t="n">
         <v>5</v>
       </c>
-      <c r="K419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -17843,12 +17391,9 @@
           <t>Pante Macassar</t>
         </is>
       </c>
-      <c r="H420" t="inlineStr"/>
-      <c r="I420" t="inlineStr"/>
       <c r="J420" t="n">
         <v>4</v>
       </c>
-      <c r="K420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -17884,12 +17429,9 @@
           <t>Pante Macassar</t>
         </is>
       </c>
-      <c r="H421" t="inlineStr"/>
-      <c r="I421" t="inlineStr"/>
       <c r="J421" t="n">
         <v>3</v>
       </c>
-      <c r="K421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -17925,12 +17467,9 @@
           <t>Pante Macassar</t>
         </is>
       </c>
-      <c r="H422" t="inlineStr"/>
-      <c r="I422" t="inlineStr"/>
       <c r="J422" t="n">
         <v>2</v>
       </c>
-      <c r="K422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -17966,12 +17505,9 @@
           <t>Pante Macassar</t>
         </is>
       </c>
-      <c r="H423" t="inlineStr"/>
-      <c r="I423" t="inlineStr"/>
       <c r="J423" t="n">
         <v>4</v>
       </c>
-      <c r="K423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -18007,12 +17543,9 @@
           <t>Pante Macassar</t>
         </is>
       </c>
-      <c r="H424" t="inlineStr"/>
-      <c r="I424" t="inlineStr"/>
       <c r="J424" t="n">
         <v>2</v>
       </c>
-      <c r="K424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -18048,12 +17581,9 @@
           <t>Pante Macassar</t>
         </is>
       </c>
-      <c r="H425" t="inlineStr"/>
-      <c r="I425" t="inlineStr"/>
       <c r="J425" t="n">
         <v>4</v>
       </c>
-      <c r="K425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -18089,12 +17619,9 @@
           <t>Nitibe</t>
         </is>
       </c>
-      <c r="H426" t="inlineStr"/>
-      <c r="I426" t="inlineStr"/>
       <c r="J426" t="n">
         <v>3</v>
       </c>
-      <c r="K426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -18130,12 +17657,9 @@
           <t>Nitibe</t>
         </is>
       </c>
-      <c r="H427" t="inlineStr"/>
-      <c r="I427" t="inlineStr"/>
       <c r="J427" t="n">
         <v>3</v>
       </c>
-      <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -18171,12 +17695,9 @@
           <t>Nitibe</t>
         </is>
       </c>
-      <c r="H428" t="inlineStr"/>
-      <c r="I428" t="inlineStr"/>
       <c r="J428" t="n">
         <v>4</v>
       </c>
-      <c r="K428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -18212,12 +17733,9 @@
           <t>Nitibe</t>
         </is>
       </c>
-      <c r="H429" t="inlineStr"/>
-      <c r="I429" t="inlineStr"/>
       <c r="J429" t="n">
         <v>3</v>
       </c>
-      <c r="K429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -18253,12 +17771,9 @@
           <t>Nitibe</t>
         </is>
       </c>
-      <c r="H430" t="inlineStr"/>
-      <c r="I430" t="inlineStr"/>
       <c r="J430" t="n">
         <v>4</v>
       </c>
-      <c r="K430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -18294,12 +17809,9 @@
           <t>Oesilo</t>
         </is>
       </c>
-      <c r="H431" t="inlineStr"/>
-      <c r="I431" t="inlineStr"/>
       <c r="J431" t="n">
         <v>9</v>
       </c>
-      <c r="K431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -18335,12 +17847,9 @@
           <t>Oesilo</t>
         </is>
       </c>
-      <c r="H432" t="inlineStr"/>
-      <c r="I432" t="inlineStr"/>
       <c r="J432" t="n">
         <v>1</v>
       </c>
-      <c r="K432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -18376,12 +17885,9 @@
           <t>Oesilo</t>
         </is>
       </c>
-      <c r="H433" t="inlineStr"/>
-      <c r="I433" t="inlineStr"/>
       <c r="J433" t="n">
         <v>3</v>
       </c>
-      <c r="K433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -18417,12 +17923,9 @@
           <t>Passabe</t>
         </is>
       </c>
-      <c r="H434" t="inlineStr"/>
-      <c r="I434" t="inlineStr"/>
       <c r="J434" t="n">
         <v>3</v>
       </c>
-      <c r="K434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -18458,12 +17961,9 @@
           <t>Passabe</t>
         </is>
       </c>
-      <c r="H435" t="inlineStr"/>
-      <c r="I435" t="inlineStr"/>
       <c r="J435" t="n">
         <v>1</v>
       </c>
-      <c r="K435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -18499,12 +17999,9 @@
           <t>Viqueque</t>
         </is>
       </c>
-      <c r="H436" t="inlineStr"/>
-      <c r="I436" t="inlineStr"/>
       <c r="J436" t="n">
         <v>6</v>
       </c>
-      <c r="K436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -18540,12 +18037,9 @@
           <t>Viqueque</t>
         </is>
       </c>
-      <c r="H437" t="inlineStr"/>
-      <c r="I437" t="inlineStr"/>
       <c r="J437" t="n">
         <v>8</v>
       </c>
-      <c r="K437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -18581,12 +18075,9 @@
           <t>Viqueque</t>
         </is>
       </c>
-      <c r="H438" t="inlineStr"/>
-      <c r="I438" t="inlineStr"/>
       <c r="J438" t="n">
         <v>7</v>
       </c>
-      <c r="K438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -18622,12 +18113,9 @@
           <t>Viqueque</t>
         </is>
       </c>
-      <c r="H439" t="inlineStr"/>
-      <c r="I439" t="inlineStr"/>
       <c r="J439" t="n">
         <v>3</v>
       </c>
-      <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -18663,12 +18151,9 @@
           <t>Viqueque</t>
         </is>
       </c>
-      <c r="H440" t="inlineStr"/>
-      <c r="I440" t="inlineStr"/>
       <c r="J440" t="n">
         <v>4</v>
       </c>
-      <c r="K440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -18704,12 +18189,9 @@
           <t>Viqueque</t>
         </is>
       </c>
-      <c r="H441" t="inlineStr"/>
-      <c r="I441" t="inlineStr"/>
       <c r="J441" t="n">
         <v>3</v>
       </c>
-      <c r="K441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -18745,12 +18227,9 @@
           <t>Viqueque</t>
         </is>
       </c>
-      <c r="H442" t="inlineStr"/>
-      <c r="I442" t="inlineStr"/>
       <c r="J442" t="n">
         <v>6</v>
       </c>
-      <c r="K442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -18786,12 +18265,9 @@
           <t>Viqueque</t>
         </is>
       </c>
-      <c r="H443" t="inlineStr"/>
-      <c r="I443" t="inlineStr"/>
       <c r="J443" t="n">
         <v>9</v>
       </c>
-      <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -18827,12 +18303,9 @@
           <t>Viqueque</t>
         </is>
       </c>
-      <c r="H444" t="inlineStr"/>
-      <c r="I444" t="inlineStr"/>
       <c r="J444" t="n">
         <v>8</v>
       </c>
-      <c r="K444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -18868,12 +18341,9 @@
           <t>Viqueque</t>
         </is>
       </c>
-      <c r="H445" t="inlineStr"/>
-      <c r="I445" t="inlineStr"/>
       <c r="J445" t="n">
         <v>8</v>
       </c>
-      <c r="K445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -18909,12 +18379,9 @@
           <t>Ossu</t>
         </is>
       </c>
-      <c r="H446" t="inlineStr"/>
-      <c r="I446" t="inlineStr"/>
       <c r="J446" t="n">
         <v>5</v>
       </c>
-      <c r="K446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -18950,12 +18417,9 @@
           <t>Ossu</t>
         </is>
       </c>
-      <c r="H447" t="inlineStr"/>
-      <c r="I447" t="inlineStr"/>
       <c r="J447" t="n">
         <v>4</v>
       </c>
-      <c r="K447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -18991,12 +18455,9 @@
           <t>Ossu</t>
         </is>
       </c>
-      <c r="H448" t="inlineStr"/>
-      <c r="I448" t="inlineStr"/>
       <c r="J448" t="n">
         <v>5</v>
       </c>
-      <c r="K448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -19032,12 +18493,9 @@
           <t>Ossu</t>
         </is>
       </c>
-      <c r="H449" t="inlineStr"/>
-      <c r="I449" t="inlineStr"/>
       <c r="J449" t="n">
         <v>5</v>
       </c>
-      <c r="K449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -19073,12 +18531,9 @@
           <t>Ossu</t>
         </is>
       </c>
-      <c r="H450" t="inlineStr"/>
-      <c r="I450" t="inlineStr"/>
       <c r="J450" t="n">
         <v>5</v>
       </c>
-      <c r="K450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -19114,12 +18569,9 @@
           <t>Ossu</t>
         </is>
       </c>
-      <c r="H451" t="inlineStr"/>
-      <c r="I451" t="inlineStr"/>
       <c r="J451" t="n">
         <v>8</v>
       </c>
-      <c r="K451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -19155,12 +18607,9 @@
           <t>Ossu</t>
         </is>
       </c>
-      <c r="H452" t="inlineStr"/>
-      <c r="I452" t="inlineStr"/>
       <c r="J452" t="n">
         <v>8</v>
       </c>
-      <c r="K452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -19196,12 +18645,9 @@
           <t>Ossu</t>
         </is>
       </c>
-      <c r="H453" t="inlineStr"/>
-      <c r="I453" t="inlineStr"/>
       <c r="J453" t="n">
         <v>6</v>
       </c>
-      <c r="K453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -19237,53 +18683,62 @@
           <t>Ossu</t>
         </is>
       </c>
-      <c r="H454" t="inlineStr"/>
-      <c r="I454" t="inlineStr"/>
       <c r="J454" t="n">
         <v>6</v>
       </c>
-      <c r="K454" t="inlineStr"/>
     </row>
     <row r="455">
-      <c r="A455" s="4" t="inlineStr">
+      <c r="A455" s="5" t="inlineStr">
         <is>
           <t>VIQ</t>
         </is>
       </c>
-      <c r="B455" s="4" t="inlineStr">
+      <c r="B455" s="5" t="inlineStr">
         <is>
           <t>Viqueque</t>
         </is>
       </c>
-      <c r="C455" s="4" t="n">
+      <c r="C455" s="5" t="n">
         <v>454</v>
       </c>
-      <c r="D455" s="4" t="inlineStr">
+      <c r="D455" s="5" t="inlineStr">
         <is>
           <t>VIQ-S454</t>
         </is>
       </c>
-      <c r="E455" s="4" t="inlineStr">
+      <c r="E455" s="5" t="inlineStr">
         <is>
           <t>Uaibobo</t>
         </is>
       </c>
-      <c r="F455" s="4" t="inlineStr"/>
-      <c r="G455" s="4" t="inlineStr"/>
-      <c r="H455" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I455" s="4" t="inlineStr">
+      <c r="F455" s="5" t="inlineStr">
+        <is>
+          <t>VIQ-02</t>
+        </is>
+      </c>
+      <c r="G455" s="5" t="inlineStr">
+        <is>
+          <t>Ossu</t>
+        </is>
+      </c>
+      <c r="H455" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I455" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: VIQ-04 Uatolari / VIQ-02 Ossu</t>
         </is>
       </c>
-      <c r="J455" s="4" t="n">
+      <c r="J455" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="K455" s="4" t="inlineStr"/>
+      <c r="K455" s="5" t="inlineStr">
+        <is>
+          <t>Fonte postu: https://wikipedia.jakami.de/content/wikipedia_de_all_mini_2024-06/A/Uaibobo</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -19319,8 +18774,6 @@
           <t>Uatolari</t>
         </is>
       </c>
-      <c r="H456" t="inlineStr"/>
-      <c r="I456" t="inlineStr"/>
       <c r="J456" t="n">
         <v>10</v>
       </c>
@@ -19364,12 +18817,9 @@
           <t>Uatolari</t>
         </is>
       </c>
-      <c r="H457" t="inlineStr"/>
-      <c r="I457" t="inlineStr"/>
       <c r="J457" t="n">
         <v>8</v>
       </c>
-      <c r="K457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -19405,12 +18855,9 @@
           <t>Uatolari</t>
         </is>
       </c>
-      <c r="H458" t="inlineStr"/>
-      <c r="I458" t="inlineStr"/>
       <c r="J458" t="n">
         <v>7</v>
       </c>
-      <c r="K458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -19446,12 +18893,9 @@
           <t>Uatolari</t>
         </is>
       </c>
-      <c r="H459" t="inlineStr"/>
-      <c r="I459" t="inlineStr"/>
       <c r="J459" t="n">
         <v>12</v>
       </c>
-      <c r="K459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -19487,12 +18931,9 @@
           <t>Uatolari</t>
         </is>
       </c>
-      <c r="H460" t="inlineStr"/>
-      <c r="I460" t="inlineStr"/>
       <c r="J460" t="n">
         <v>8</v>
       </c>
-      <c r="K460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -19528,12 +18969,9 @@
           <t>Uatolari</t>
         </is>
       </c>
-      <c r="H461" t="inlineStr"/>
-      <c r="I461" t="inlineStr"/>
       <c r="J461" t="n">
         <v>6</v>
       </c>
-      <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -19569,12 +19007,9 @@
           <t>Uatolari</t>
         </is>
       </c>
-      <c r="H462" t="inlineStr"/>
-      <c r="I462" t="inlineStr"/>
       <c r="J462" t="n">
         <v>5</v>
       </c>
-      <c r="K462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -19610,55 +19045,60 @@
           <t>Uatolari</t>
         </is>
       </c>
-      <c r="H463" t="inlineStr"/>
-      <c r="I463" t="inlineStr"/>
       <c r="J463" t="n">
         <v>7</v>
       </c>
-      <c r="K463" t="inlineStr"/>
     </row>
     <row r="464">
-      <c r="A464" s="4" t="inlineStr">
+      <c r="A464" s="5" t="inlineStr">
         <is>
           <t>VIQ</t>
         </is>
       </c>
-      <c r="B464" s="4" t="inlineStr">
+      <c r="B464" s="5" t="inlineStr">
         <is>
           <t>Viqueque</t>
         </is>
       </c>
-      <c r="C464" s="4" t="n">
+      <c r="C464" s="5" t="n">
         <v>463</v>
       </c>
-      <c r="D464" s="4" t="inlineStr">
+      <c r="D464" s="5" t="inlineStr">
         <is>
           <t>VIQ-S463</t>
         </is>
       </c>
-      <c r="E464" s="4" t="inlineStr">
+      <c r="E464" s="5" t="inlineStr">
         <is>
           <t>Afaloicai</t>
         </is>
       </c>
-      <c r="F464" s="4" t="inlineStr"/>
-      <c r="G464" s="4" t="inlineStr"/>
-      <c r="H464" s="4" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="I464" s="4" t="inlineStr">
+      <c r="F464" s="5" t="inlineStr">
+        <is>
+          <t>VIQ-03</t>
+        </is>
+      </c>
+      <c r="G464" s="5" t="inlineStr">
+        <is>
+          <t>Uatucarbau</t>
+        </is>
+      </c>
+      <c r="H464" s="5" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
+      <c r="I464" s="5" t="inlineStr">
         <is>
           <t>Suco iha fronteira entre posto rua. Hili: VIQ-04 Uatolari / VIQ-03 Uatucarbau</t>
         </is>
       </c>
-      <c r="J464" s="4" t="n">
+      <c r="J464" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K464" s="4" t="inlineStr">
-        <is>
-          <t>Naran hanesan ho suco seluk iha munisípiu ne'e (kódigu la hanesan; PDF la hakerek I/II)</t>
+      <c r="K464" s="5" t="inlineStr">
+        <is>
+          <t>Naran hanesan ho suco seluk iha munisípiu ne'e (kódigu la hanesan; PDF la hakerek I/II); Afaloicai seluk (VIQ-S455) iha Uatolari; Fonte postu: https://en.wikipedia.org/wiki/Uatucarbau_Administrative_Post</t>
         </is>
       </c>
     </row>
@@ -19696,12 +19136,9 @@
           <t>Uatucarbau</t>
         </is>
       </c>
-      <c r="H465" t="inlineStr"/>
-      <c r="I465" t="inlineStr"/>
       <c r="J465" t="n">
         <v>4</v>
       </c>
-      <c r="K465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -19737,12 +19174,9 @@
           <t>Uatucarbau</t>
         </is>
       </c>
-      <c r="H466" t="inlineStr"/>
-      <c r="I466" t="inlineStr"/>
       <c r="J466" t="n">
         <v>5</v>
       </c>
-      <c r="K466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -19778,12 +19212,9 @@
           <t>Uatucarbau</t>
         </is>
       </c>
-      <c r="H467" t="inlineStr"/>
-      <c r="I467" t="inlineStr"/>
       <c r="J467" t="n">
         <v>7</v>
       </c>
-      <c r="K467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -19819,12 +19250,9 @@
           <t>Uatucarbau</t>
         </is>
       </c>
-      <c r="H468" t="inlineStr"/>
-      <c r="I468" t="inlineStr"/>
       <c r="J468" t="n">
         <v>5</v>
       </c>
-      <c r="K468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -19860,12 +19288,9 @@
           <t>Uatucarbau</t>
         </is>
       </c>
-      <c r="H469" t="inlineStr"/>
-      <c r="I469" t="inlineStr"/>
       <c r="J469" t="n">
         <v>5</v>
       </c>
-      <c r="K469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -19901,12 +19326,9 @@
           <t>Lacluta</t>
         </is>
       </c>
-      <c r="H470" t="inlineStr"/>
-      <c r="I470" t="inlineStr"/>
       <c r="J470" t="n">
         <v>5</v>
       </c>
-      <c r="K470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -19942,12 +19364,9 @@
           <t>Lacluta</t>
         </is>
       </c>
-      <c r="H471" t="inlineStr"/>
-      <c r="I471" t="inlineStr"/>
       <c r="J471" t="n">
         <v>5</v>
       </c>
-      <c r="K471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -19983,12 +19402,9 @@
           <t>Lacluta</t>
         </is>
       </c>
-      <c r="H472" t="inlineStr"/>
-      <c r="I472" t="inlineStr"/>
       <c r="J472" t="n">
         <v>5</v>
       </c>
-      <c r="K472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -20024,12 +19440,9 @@
           <t>Lacluta</t>
         </is>
       </c>
-      <c r="H473" t="inlineStr"/>
-      <c r="I473" t="inlineStr"/>
       <c r="J473" t="n">
         <v>5</v>
       </c>
-      <c r="K473" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K473"/>
@@ -65138,7 +64551,6 @@
           <t>Aileu Vila</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -65156,7 +64568,6 @@
           <t>Laulara</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -65174,7 +64585,6 @@
           <t>Lequidoe</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -65192,7 +64602,6 @@
           <t>Remexio</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -65210,7 +64619,6 @@
           <t>Ainaro</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -65228,7 +64636,6 @@
           <t>Hatu-Builico</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -65246,7 +64653,6 @@
           <t>Hatudo</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -65264,7 +64670,6 @@
           <t>Maubisse</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -65282,7 +64687,6 @@
           <t>Ataúro</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -65300,7 +64704,6 @@
           <t>Baguia</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -65318,7 +64721,6 @@
           <t>Baucau</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -65336,7 +64738,6 @@
           <t>Laga</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -65354,7 +64755,6 @@
           <t>Quelicai</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -65372,7 +64772,6 @@
           <t>Vemasse</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -65390,7 +64789,6 @@
           <t>Venilale</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -65408,7 +64806,6 @@
           <t>Atabae</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -65426,7 +64823,6 @@
           <t>Balibo</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -65444,7 +64840,6 @@
           <t>Bobonaro</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -65462,7 +64857,6 @@
           <t>Cailaco</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -65480,7 +64874,6 @@
           <t>Lolotoe</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -65498,7 +64891,6 @@
           <t>Maliana</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -65516,7 +64908,6 @@
           <t>Fatululic</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -65534,7 +64925,6 @@
           <t>Fatumean</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -65552,7 +64942,6 @@
           <t>Fohorem</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -65570,7 +64959,6 @@
           <t>Maucatar</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -65588,7 +64976,6 @@
           <t>Suai</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -65606,7 +64993,6 @@
           <t>Tilomar</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -65624,7 +65010,6 @@
           <t>Zumalai</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -65642,7 +65027,6 @@
           <t>Cristo Rei</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -65660,7 +65044,6 @@
           <t>Dom Aleixo</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -65678,7 +65061,6 @@
           <t>Metinaro</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -65696,7 +65078,6 @@
           <t>Nain Feto</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -65714,7 +65095,6 @@
           <t>Vera Cruz</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -65732,7 +65112,6 @@
           <t>Atsabe</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -65750,7 +65129,6 @@
           <t>Ermera</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -65768,7 +65146,6 @@
           <t>Hatulia</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -65786,7 +65163,6 @@
           <t>Letefoho</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -65804,7 +65180,6 @@
           <t>Railaco</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -65822,7 +65197,6 @@
           <t>Iliomar</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -65840,7 +65214,6 @@
           <t>Lautém</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -65858,7 +65231,6 @@
           <t>Lospalos</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -65876,7 +65248,6 @@
           <t>Luro</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -65894,7 +65265,6 @@
           <t>Tutuala</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -65912,7 +65282,6 @@
           <t>Bazartete</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -65930,7 +65299,6 @@
           <t>Liquiçá</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -65948,7 +65316,6 @@
           <t>Maubara</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -65966,7 +65333,6 @@
           <t>Barique</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -65984,7 +65350,6 @@
           <t>Laclo</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -66002,7 +65367,6 @@
           <t>Laclubar</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -66020,7 +65384,6 @@
           <t>Laleia</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -66038,7 +65401,6 @@
           <t>Manatuto</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -66056,7 +65418,6 @@
           <t>Soibada</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -66074,7 +65435,6 @@
           <t>Alas</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -66092,7 +65452,6 @@
           <t>Fatuberlio</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -66110,7 +65469,6 @@
           <t>Same</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -66128,7 +65486,6 @@
           <t>Turiscai</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -66146,7 +65503,6 @@
           <t>Nitibe</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -66164,7 +65520,6 @@
           <t>Oesilo</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -66182,7 +65537,6 @@
           <t>Pante Macassar</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -66200,7 +65554,6 @@
           <t>Passabe</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -66218,7 +65571,6 @@
           <t>Lacluta</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -66236,7 +65588,6 @@
           <t>Ossu</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -66254,7 +65605,6 @@
           <t>Uatucarbau</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -66272,7 +65622,6 @@
           <t>Uatolari</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -66290,7 +65639,6 @@
           <t>Viqueque</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
